--- a/output1/NeuralNetwork_val_predictions.xlsx
+++ b/output1/NeuralNetwork_val_predictions.xlsx
@@ -497,7 +497,7 @@
         <v>0.9473684210526316</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9163745238286863</v>
+        <v>0.907939236007368</v>
       </c>
     </row>
     <row r="3">
@@ -527,7 +527,7 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7497406147330856</v>
+        <v>0.01581519454303671</v>
       </c>
     </row>
     <row r="4">
@@ -557,7 +557,7 @@
         <v>3.342105263157895</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1603248419050754</v>
+        <v>0.0132737095291713</v>
       </c>
     </row>
     <row r="5">
@@ -587,7 +587,7 @@
         <v>0.5526315789473685</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8812935488749034</v>
+        <v>0.9313672485286504</v>
       </c>
     </row>
     <row r="6">
@@ -617,7 +617,7 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="H6" t="n">
-        <v>9.956231226800346e-08</v>
+        <v>5.841560200766907e-06</v>
       </c>
     </row>
     <row r="7">
@@ -647,7 +647,7 @@
         <v>1.789473684210526</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1670152586919278</v>
+        <v>0.01179494491093243</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         <v>1.947368421052632</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02297697107437441</v>
+        <v>0.4183081217572778</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +707,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2599345593519806</v>
+        <v>0.007159758014819522</v>
       </c>
     </row>
     <row r="10">
@@ -737,7 +737,7 @@
         <v>2.868421052631579</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2052416434291057</v>
+        <v>0.421416909078368</v>
       </c>
     </row>
     <row r="11">
@@ -767,7 +767,7 @@
         <v>0.4736842105263157</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9994340803117605</v>
+        <v>0.5131668982371019</v>
       </c>
     </row>
     <row r="12">
@@ -797,7 +797,7 @@
         <v>2.894736842105264</v>
       </c>
       <c r="H12" t="n">
-        <v>1.500206270615024e-05</v>
+        <v>0.007525237786767345</v>
       </c>
     </row>
     <row r="13">
@@ -824,10 +824,10 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3.868421052631578</v>
+        <v>3.868421052631577</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003723554166901457</v>
+        <v>0.5304995165896156</v>
       </c>
     </row>
     <row r="14">
@@ -857,7 +857,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4920923018394805</v>
+        <v>0.9879234102266682</v>
       </c>
     </row>
     <row r="15">
@@ -887,7 +887,7 @@
         <v>7.657894736842105</v>
       </c>
       <c r="H15" t="n">
-        <v>0.999999999996634</v>
+        <v>0.9989616605685052</v>
       </c>
     </row>
     <row r="16">
@@ -917,7 +917,7 @@
         <v>4.552631578947368</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9644469457243183</v>
+        <v>0.7310886354035928</v>
       </c>
     </row>
     <row r="17">
@@ -947,7 +947,7 @@
         <v>1.710526315789474</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0009689595467220302</v>
+        <v>0.0009012725076238709</v>
       </c>
     </row>
     <row r="18">
@@ -977,7 +977,7 @@
         <v>2.789473684210526</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8845234872559465</v>
+        <v>0.5527268593707459</v>
       </c>
     </row>
     <row r="19">
@@ -1007,7 +1007,7 @@
         <v>2.473684210526316</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9999606021923363</v>
+        <v>0.9999365231550329</v>
       </c>
     </row>
     <row r="20">
@@ -1037,7 +1037,7 @@
         <v>1.684210526315789</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3738387425105198</v>
+        <v>0.06663775940640261</v>
       </c>
     </row>
     <row r="21">
@@ -1067,7 +1067,7 @@
         <v>1.026315789473684</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9110820974964856</v>
+        <v>0.7584688380190412</v>
       </c>
     </row>
     <row r="22">
@@ -1097,7 +1097,7 @@
         <v>0.6842105263157895</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02149649660956709</v>
+        <v>0.1320400656084852</v>
       </c>
     </row>
     <row r="23">
@@ -1127,7 +1127,7 @@
         <v>3.131578947368421</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9890429824984825</v>
+        <v>0.9604303529708824</v>
       </c>
     </row>
     <row r="24">
@@ -1157,7 +1157,7 @@
         <v>1.473684210526316</v>
       </c>
       <c r="H24" t="n">
-        <v>0.147778663455788</v>
+        <v>0.1881550920747456</v>
       </c>
     </row>
     <row r="25">
@@ -1187,7 +1187,7 @@
         <v>1.236842105263158</v>
       </c>
       <c r="H25" t="n">
-        <v>0.948660028483084</v>
+        <v>0.9772254249540747</v>
       </c>
     </row>
     <row r="26">
@@ -1217,7 +1217,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9671478864046178</v>
+        <v>0.1512246689947432</v>
       </c>
     </row>
     <row r="27">
@@ -1247,7 +1247,7 @@
         <v>2.736842105263158</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9931787567187292</v>
+        <v>0.9992936600492972</v>
       </c>
     </row>
     <row r="28">
@@ -1277,7 +1277,7 @@
         <v>2.605263157894737</v>
       </c>
       <c r="H28" t="n">
-        <v>0.004205958231173803</v>
+        <v>0.3562148861483257</v>
       </c>
     </row>
     <row r="29">
@@ -1307,7 +1307,7 @@
         <v>1.578947368421053</v>
       </c>
       <c r="H29" t="n">
-        <v>0.003263142154343269</v>
+        <v>0.002726103880993812</v>
       </c>
     </row>
     <row r="30">
@@ -1337,7 +1337,7 @@
         <v>6.473684210526316</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1807093656092799</v>
+        <v>0.1807093656092796</v>
       </c>
     </row>
     <row r="31">
@@ -1367,7 +1367,7 @@
         <v>6.342105263157895</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5657991816050559</v>
+        <v>0.5657991816050556</v>
       </c>
     </row>
     <row r="32">
@@ -1457,7 +1457,7 @@
         <v>21.68421052631579</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09883260708323181</v>
+        <v>0.09883260708323184</v>
       </c>
     </row>
     <row r="35">
@@ -1517,7 +1517,7 @@
         <v>1.894736842105263</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9343169472103906</v>
+        <v>0.8781174034574605</v>
       </c>
     </row>
     <row r="37">
@@ -1547,7 +1547,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9194001865689474</v>
+        <v>0.9194001865689472</v>
       </c>
     </row>
     <row r="38">
@@ -1577,7 +1577,7 @@
         <v>1.894736842105263</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5137771317245244</v>
+        <v>0.5137771317245245</v>
       </c>
     </row>
     <row r="39">
@@ -1667,7 +1667,7 @@
         <v>111.421052631579</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03496776708483769</v>
+        <v>0.03496776708483774</v>
       </c>
     </row>
     <row r="42">
@@ -1697,7 +1697,7 @@
         <v>15.02631578947368</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04121466765780735</v>
+        <v>0.04121466765780742</v>
       </c>
     </row>
     <row r="43">
@@ -1727,7 +1727,7 @@
         <v>19.34210526315789</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9568311866667949</v>
+        <v>0.9568311866667951</v>
       </c>
     </row>
     <row r="44">
@@ -1787,7 +1787,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2163048732464141</v>
+        <v>0.2163048732464142</v>
       </c>
     </row>
     <row r="46">
@@ -1817,7 +1817,7 @@
         <v>7.263157894736842</v>
       </c>
       <c r="H46" t="n">
-        <v>0.03009856770868983</v>
+        <v>0.03009856770868988</v>
       </c>
     </row>
     <row r="47">
@@ -1907,7 +1907,7 @@
         <v>0.7631578947368421</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0001428457026723295</v>
+        <v>0.0001428457026723305</v>
       </c>
     </row>
     <row r="50">
@@ -1937,7 +1937,7 @@
         <v>164.4473684210526</v>
       </c>
       <c r="H50" t="n">
-        <v>3.141044431270218e-13</v>
+        <v>3.141044431270252e-13</v>
       </c>
     </row>
     <row r="51">
@@ -1967,7 +1967,7 @@
         <v>2.210526315789474</v>
       </c>
       <c r="H51" t="n">
-        <v>4.741525853903699e-06</v>
+        <v>4.741525853903707e-06</v>
       </c>
     </row>
     <row r="52">
@@ -2027,7 +2027,7 @@
         <v>3.184210526315789</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9730685744279647</v>
+        <v>0.9730685744279645</v>
       </c>
     </row>
     <row r="54">
@@ -2057,7 +2057,7 @@
         <v>4.888268156424582</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3701288524212498</v>
+        <v>0.1753207182093469</v>
       </c>
     </row>
     <row r="55">
@@ -2087,7 +2087,7 @@
         <v>2.067039106145252</v>
       </c>
       <c r="H55" t="n">
-        <v>0.005418595033560737</v>
+        <v>0.00540156121093963</v>
       </c>
     </row>
     <row r="56">
@@ -2117,7 +2117,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H56" t="n">
-        <v>0.981818088939026</v>
+        <v>0.9831416460972877</v>
       </c>
     </row>
     <row r="57">
@@ -2147,7 +2147,7 @@
         <v>4.804469273743017</v>
       </c>
       <c r="H57" t="n">
-        <v>0.942308234199885</v>
+        <v>0.9559031842892396</v>
       </c>
     </row>
     <row r="58">
@@ -2177,7 +2177,7 @@
         <v>4.329608938547486</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2541220674759689</v>
+        <v>0.1846285454029268</v>
       </c>
     </row>
     <row r="59">
@@ -2207,7 +2207,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H59" t="n">
-        <v>0.7205212153466971</v>
+        <v>0.5899798115536812</v>
       </c>
     </row>
     <row r="60">
@@ -2237,7 +2237,7 @@
         <v>4.189944134078212</v>
       </c>
       <c r="H60" t="n">
-        <v>0.00693666840031223</v>
+        <v>0.009042109122646226</v>
       </c>
     </row>
     <row r="61">
@@ -2267,7 +2267,7 @@
         <v>5.363128491620112</v>
       </c>
       <c r="H61" t="n">
-        <v>0.003279228315732083</v>
+        <v>0.002567907331832371</v>
       </c>
     </row>
     <row r="62">
@@ -2297,7 +2297,7 @@
         <v>21.08938547486034</v>
       </c>
       <c r="H62" t="n">
-        <v>0.9853297028713185</v>
+        <v>0.9793471937072873</v>
       </c>
     </row>
     <row r="63">
@@ -2327,7 +2327,7 @@
         <v>28.46368715083799</v>
       </c>
       <c r="H63" t="n">
-        <v>0.9992531362369333</v>
+        <v>0.9997646385594094</v>
       </c>
     </row>
     <row r="64">
@@ -2357,7 +2357,7 @@
         <v>14.41340782122905</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1868857187135121</v>
+        <v>0.6901784196770527</v>
       </c>
     </row>
     <row r="65">
@@ -2387,7 +2387,7 @@
         <v>25.19553072625699</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9964145548134117</v>
+        <v>0.9986071935788918</v>
       </c>
     </row>
     <row r="66">
@@ -2417,7 +2417,7 @@
         <v>7.765363128491621</v>
       </c>
       <c r="H66" t="n">
-        <v>0.009795641487038011</v>
+        <v>0.01211315075691169</v>
       </c>
     </row>
     <row r="67">
@@ -2447,7 +2447,7 @@
         <v>16.36871508379888</v>
       </c>
       <c r="H67" t="n">
-        <v>0.998781303881108</v>
+        <v>0.9972586751321844</v>
       </c>
     </row>
     <row r="68">
@@ -2477,7 +2477,7 @@
         <v>8</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0001119855977955808</v>
+        <v>4.779793711681018e-06</v>
       </c>
     </row>
     <row r="69">
@@ -2507,7 +2507,7 @@
         <v>8</v>
       </c>
       <c r="H69" t="n">
-        <v>0.003097820413174021</v>
+        <v>0.1261007755229369</v>
       </c>
     </row>
     <row r="70">
@@ -2537,7 +2537,7 @@
         <v>10</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9864533314295675</v>
+        <v>0.8270915271591276</v>
       </c>
     </row>
     <row r="71">
@@ -2567,7 +2567,7 @@
         <v>38</v>
       </c>
       <c r="H71" t="n">
-        <v>0.008391056104256079</v>
+        <v>0.3172347657110748</v>
       </c>
     </row>
     <row r="72">
@@ -2597,7 +2597,7 @@
         <v>5</v>
       </c>
       <c r="H72" t="n">
-        <v>6.557723492365402e-06</v>
+        <v>6.203623098678869e-06</v>
       </c>
     </row>
     <row r="73">
@@ -2627,7 +2627,7 @@
         <v>19</v>
       </c>
       <c r="H73" t="n">
-        <v>0.01015775685733699</v>
+        <v>0.01712433414647087</v>
       </c>
     </row>
     <row r="74">
@@ -2657,7 +2657,7 @@
         <v>16</v>
       </c>
       <c r="H74" t="n">
-        <v>0.6026804030313113</v>
+        <v>0.9188717090959166</v>
       </c>
     </row>
     <row r="75">
@@ -2687,7 +2687,7 @@
         <v>5</v>
       </c>
       <c r="H75" t="n">
-        <v>1.755746349782011e-06</v>
+        <v>2.375040000369798e-05</v>
       </c>
     </row>
     <row r="76">
@@ -2717,7 +2717,7 @@
         <v>8</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1446851938047766</v>
+        <v>0.002017560479079265</v>
       </c>
     </row>
     <row r="77">
@@ -2747,7 +2747,7 @@
         <v>13</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0002336943874621873</v>
+        <v>0.0009794701983041859</v>
       </c>
     </row>
     <row r="78">
@@ -2777,7 +2777,7 @@
         <v>8</v>
       </c>
       <c r="H78" t="n">
-        <v>0.001690685869632738</v>
+        <v>0.00147823319473879</v>
       </c>
     </row>
     <row r="79">
@@ -2807,7 +2807,7 @@
         <v>6</v>
       </c>
       <c r="H79" t="n">
-        <v>0.001181340576089988</v>
+        <v>8.9667860668896e-05</v>
       </c>
     </row>
     <row r="80">
@@ -2837,7 +2837,7 @@
         <v>9</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0003535544084381054</v>
+        <v>0.01054571640020606</v>
       </c>
     </row>
     <row r="81">
@@ -2867,7 +2867,7 @@
         <v>8</v>
       </c>
       <c r="H81" t="n">
-        <v>0.001578967518775293</v>
+        <v>0.0003597711514636245</v>
       </c>
     </row>
     <row r="82">
@@ -2897,7 +2897,7 @@
         <v>14</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9953284299252139</v>
+        <v>0.9923839788113969</v>
       </c>
     </row>
     <row r="83">
@@ -2927,7 +2927,7 @@
         <v>8</v>
       </c>
       <c r="H83" t="n">
-        <v>5.152399636366619e-08</v>
+        <v>2.621324681898385e-05</v>
       </c>
     </row>
     <row r="84">
@@ -2957,7 +2957,7 @@
         <v>6</v>
       </c>
       <c r="H84" t="n">
-        <v>1.898644237741128e-06</v>
+        <v>6.543848079863614e-09</v>
       </c>
     </row>
     <row r="85">
@@ -2987,7 +2987,7 @@
         <v>5</v>
       </c>
       <c r="H85" t="n">
-        <v>0.01185622562872122</v>
+        <v>1.174446236504526e-06</v>
       </c>
     </row>
     <row r="86">
@@ -3017,7 +3017,7 @@
         <v>15</v>
       </c>
       <c r="H86" t="n">
-        <v>0.7143219843855616</v>
+        <v>0.3394719152061849</v>
       </c>
     </row>
     <row r="87">
@@ -3047,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="H87" t="n">
-        <v>0.003381396633439235</v>
+        <v>0.0002617974376047685</v>
       </c>
     </row>
     <row r="88">
@@ -3077,7 +3077,7 @@
         <v>8</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0002112383212068119</v>
+        <v>0.0008908290704254126</v>
       </c>
     </row>
     <row r="89">
@@ -3107,7 +3107,7 @@
         <v>10</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0004525959776705692</v>
+        <v>0.0003233153760226387</v>
       </c>
     </row>
     <row r="90">
@@ -3137,7 +3137,7 @@
         <v>21</v>
       </c>
       <c r="H90" t="n">
-        <v>0.9952059122166634</v>
+        <v>0.9980734188673708</v>
       </c>
     </row>
     <row r="91">
@@ -3167,7 +3167,7 @@
         <v>8</v>
       </c>
       <c r="H91" t="n">
-        <v>0.00180326483300053</v>
+        <v>0.004820394444222653</v>
       </c>
     </row>
     <row r="92">
@@ -3197,7 +3197,7 @@
         <v>5</v>
       </c>
       <c r="H92" t="n">
-        <v>0.003126124401189961</v>
+        <v>0.0006158428396911232</v>
       </c>
     </row>
     <row r="93">
@@ -3227,7 +3227,7 @@
         <v>4</v>
       </c>
       <c r="H93" t="n">
-        <v>7.245595793308822e-05</v>
+        <v>0.002081204078001322</v>
       </c>
     </row>
     <row r="94">
@@ -3257,7 +3257,7 @@
         <v>17</v>
       </c>
       <c r="H94" t="n">
-        <v>0.3346338660558131</v>
+        <v>0.9967494396633821</v>
       </c>
     </row>
     <row r="95">
@@ -3287,7 +3287,7 @@
         <v>6</v>
       </c>
       <c r="H95" t="n">
-        <v>0.007054376846276943</v>
+        <v>0.004094575010892334</v>
       </c>
     </row>
     <row r="96">
@@ -3317,7 +3317,7 @@
         <v>6</v>
       </c>
       <c r="H96" t="n">
-        <v>0.04011464157844453</v>
+        <v>0.1484809082095241</v>
       </c>
     </row>
     <row r="97">
@@ -3347,7 +3347,7 @@
         <v>8</v>
       </c>
       <c r="H97" t="n">
-        <v>0.5174321826018103</v>
+        <v>0.005623467935708868</v>
       </c>
     </row>
     <row r="98">
@@ -3377,7 +3377,7 @@
         <v>7</v>
       </c>
       <c r="H98" t="n">
-        <v>1.111244473498288e-05</v>
+        <v>5.601664204055519e-06</v>
       </c>
     </row>
     <row r="99">
@@ -3407,7 +3407,7 @@
         <v>8</v>
       </c>
       <c r="H99" t="n">
-        <v>0.0004773442468277936</v>
+        <v>0.001168434315910573</v>
       </c>
     </row>
     <row r="100">
@@ -3437,7 +3437,7 @@
         <v>8</v>
       </c>
       <c r="H100" t="n">
-        <v>0.004345665996291936</v>
+        <v>0.004055193639409397</v>
       </c>
     </row>
     <row r="101">
@@ -3467,7 +3467,7 @@
         <v>8</v>
       </c>
       <c r="H101" t="n">
-        <v>0.003523782248926456</v>
+        <v>0.000268027088474133</v>
       </c>
     </row>
     <row r="102">
@@ -3497,7 +3497,7 @@
         <v>6</v>
       </c>
       <c r="H102" t="n">
-        <v>1.382975781639162e-06</v>
+        <v>6.846424360384559e-06</v>
       </c>
     </row>
     <row r="103">
@@ -3527,7 +3527,7 @@
         <v>49</v>
       </c>
       <c r="H103" t="n">
-        <v>0.9998956904695042</v>
+        <v>0.9999953858344101</v>
       </c>
     </row>
     <row r="104">
@@ -3557,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="H104" t="n">
-        <v>8.333197154780892e-05</v>
+        <v>0.0003798442825546066</v>
       </c>
     </row>
     <row r="105">
@@ -3587,7 +3587,7 @@
         <v>11</v>
       </c>
       <c r="H105" t="n">
-        <v>6.051606462348561e-06</v>
+        <v>0.0002185306089229017</v>
       </c>
     </row>
     <row r="106">
@@ -3617,7 +3617,7 @@
         <v>22</v>
       </c>
       <c r="H106" t="n">
-        <v>0.001759062516078075</v>
+        <v>0.1381820095836974</v>
       </c>
     </row>
     <row r="107">
@@ -3647,7 +3647,7 @@
         <v>19</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1663323991898109</v>
+        <v>0.08951195551423398</v>
       </c>
     </row>
     <row r="108">
@@ -3677,7 +3677,7 @@
         <v>12</v>
       </c>
       <c r="H108" t="n">
-        <v>0.165888215027494</v>
+        <v>0.03391566575819357</v>
       </c>
     </row>
     <row r="109">
@@ -3707,7 +3707,7 @@
         <v>8</v>
       </c>
       <c r="H109" t="n">
-        <v>0.001574711771313963</v>
+        <v>0.000636598237328786</v>
       </c>
     </row>
     <row r="110">
@@ -3737,7 +3737,7 @@
         <v>3</v>
       </c>
       <c r="H110" t="n">
-        <v>0.9798771975940571</v>
+        <v>0.003220174230659546</v>
       </c>
     </row>
     <row r="111">
@@ -3767,7 +3767,7 @@
         <v>11</v>
       </c>
       <c r="H111" t="n">
-        <v>0.9060065575380568</v>
+        <v>0.9874197355006467</v>
       </c>
     </row>
     <row r="112">
@@ -3797,7 +3797,7 @@
         <v>7</v>
       </c>
       <c r="H112" t="n">
-        <v>0.7663518435296977</v>
+        <v>0.01471893745457043</v>
       </c>
     </row>
     <row r="113">
@@ -3827,7 +3827,7 @@
         <v>8</v>
       </c>
       <c r="H113" t="n">
-        <v>0.002155934542136218</v>
+        <v>7.411006121150407e-05</v>
       </c>
     </row>
     <row r="114">
@@ -3857,7 +3857,7 @@
         <v>9</v>
       </c>
       <c r="H114" t="n">
-        <v>1.309558870282855e-05</v>
+        <v>9.750113563596546e-05</v>
       </c>
     </row>
     <row r="115">
@@ -3887,7 +3887,7 @@
         <v>35</v>
       </c>
       <c r="H115" t="n">
-        <v>0.6805601559212195</v>
+        <v>0.8439481700204303</v>
       </c>
     </row>
     <row r="116">
@@ -3917,7 +3917,7 @@
         <v>5</v>
       </c>
       <c r="H116" t="n">
-        <v>0.7379460984563138</v>
+        <v>0.8112612901822837</v>
       </c>
     </row>
     <row r="117">
@@ -3947,7 +3947,7 @@
         <v>5</v>
       </c>
       <c r="H117" t="n">
-        <v>0.9981156748733701</v>
+        <v>0.9994171362819398</v>
       </c>
     </row>
     <row r="118">
@@ -3977,7 +3977,7 @@
         <v>3</v>
       </c>
       <c r="H118" t="n">
-        <v>2.640912308029131e-09</v>
+        <v>3.817517069559481e-11</v>
       </c>
     </row>
     <row r="119">
@@ -4007,7 +4007,7 @@
         <v>8</v>
       </c>
       <c r="H119" t="n">
-        <v>9.70479596627691e-05</v>
+        <v>1.417212648089241e-05</v>
       </c>
     </row>
     <row r="120">
@@ -4037,7 +4037,7 @@
         <v>8</v>
       </c>
       <c r="H120" t="n">
-        <v>0.07890909876447644</v>
+        <v>0.0307876704770336</v>
       </c>
     </row>
     <row r="121">
@@ -4067,7 +4067,7 @@
         <v>8</v>
       </c>
       <c r="H121" t="n">
-        <v>4.978905223726948e-05</v>
+        <v>3.032698001063604e-05</v>
       </c>
     </row>
     <row r="122">
@@ -4097,7 +4097,7 @@
         <v>5</v>
       </c>
       <c r="H122" t="n">
-        <v>0.0002938474976047382</v>
+        <v>0.0001736771874531077</v>
       </c>
     </row>
     <row r="123">
@@ -4127,7 +4127,7 @@
         <v>8</v>
       </c>
       <c r="H123" t="n">
-        <v>2.37623501780646e-05</v>
+        <v>0.0001156636849681455</v>
       </c>
     </row>
     <row r="124">
@@ -4157,7 +4157,7 @@
         <v>14</v>
       </c>
       <c r="H124" t="n">
-        <v>0.9998091671481316</v>
+        <v>0.9969280197922957</v>
       </c>
     </row>
     <row r="125">
@@ -4187,7 +4187,7 @@
         <v>4</v>
       </c>
       <c r="H125" t="n">
-        <v>4.640254427536114e-07</v>
+        <v>6.547411150983667e-06</v>
       </c>
     </row>
     <row r="126">
@@ -4217,7 +4217,7 @@
         <v>7</v>
       </c>
       <c r="H126" t="n">
-        <v>0.2986515552872727</v>
+        <v>0.4095785881745955</v>
       </c>
     </row>
     <row r="127">
@@ -4247,7 +4247,7 @@
         <v>10</v>
       </c>
       <c r="H127" t="n">
-        <v>0.003680309920136279</v>
+        <v>0.003260422037987674</v>
       </c>
     </row>
     <row r="128">
@@ -4277,7 +4277,7 @@
         <v>0.8947368421052632</v>
       </c>
       <c r="H128" t="n">
-        <v>0.6272867115585928</v>
+        <v>0.9775263781140562</v>
       </c>
     </row>
     <row r="129">
@@ -4307,7 +4307,7 @@
         <v>1.157894736842105</v>
       </c>
       <c r="H129" t="n">
-        <v>0.0007340922909274292</v>
+        <v>0.1962192574156296</v>
       </c>
     </row>
     <row r="130">
@@ -4337,7 +4337,7 @@
         <v>1.105263157894737</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9892364761470205</v>
+        <v>0.9998683796155029</v>
       </c>
     </row>
     <row r="131">
@@ -4367,7 +4367,7 @@
         <v>1.921052631578948</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9999999923476804</v>
+        <v>0.999912757588439</v>
       </c>
     </row>
     <row r="132">
@@ -4397,7 +4397,7 @@
         <v>0.6578947368421053</v>
       </c>
       <c r="H132" t="n">
-        <v>0.03987391225170283</v>
+        <v>0.007559878362856693</v>
       </c>
     </row>
     <row r="133">
@@ -4427,7 +4427,7 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="H133" t="n">
-        <v>0.9999491707932541</v>
+        <v>0.999921169611582</v>
       </c>
     </row>
     <row r="134">
@@ -4457,7 +4457,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1741345651808378</v>
+        <v>0.01243069652974684</v>
       </c>
     </row>
     <row r="135">
@@ -4487,7 +4487,7 @@
         <v>0.631578947368421</v>
       </c>
       <c r="H135" t="n">
-        <v>0.9255865509072695</v>
+        <v>0.8835133530400305</v>
       </c>
     </row>
     <row r="136">
@@ -4517,7 +4517,7 @@
         <v>1.789473684210526</v>
       </c>
       <c r="H136" t="n">
-        <v>0.3673740623213117</v>
+        <v>0.005292248535859493</v>
       </c>
     </row>
     <row r="137">
@@ -4547,7 +4547,7 @@
         <v>1.447368421052632</v>
       </c>
       <c r="H137" t="n">
-        <v>0.000206306705811567</v>
+        <v>0.002006251695199037</v>
       </c>
     </row>
     <row r="138">
@@ -4577,7 +4577,7 @@
         <v>4.657894736842105</v>
       </c>
       <c r="H138" t="n">
-        <v>0.9999999993882804</v>
+        <v>0.999995858754002</v>
       </c>
     </row>
     <row r="139">
@@ -4607,7 +4607,7 @@
         <v>1.710526315789474</v>
       </c>
       <c r="H139" t="n">
-        <v>0.9074678696988392</v>
+        <v>0.9800915031000683</v>
       </c>
     </row>
     <row r="140">
@@ -4637,7 +4637,7 @@
         <v>1.368421052631579</v>
       </c>
       <c r="H140" t="n">
-        <v>0.4598657132308524</v>
+        <v>0.6006798091612823</v>
       </c>
     </row>
     <row r="141">
@@ -4667,7 +4667,7 @@
         <v>2.763157894736842</v>
       </c>
       <c r="H141" t="n">
-        <v>0.4343981292536261</v>
+        <v>0.3105063507684929</v>
       </c>
     </row>
     <row r="142">
@@ -4697,7 +4697,7 @@
         <v>1.131578947368421</v>
       </c>
       <c r="H142" t="n">
-        <v>0.0266304588287852</v>
+        <v>0.1200780662292497</v>
       </c>
     </row>
     <row r="143">
@@ -4727,7 +4727,7 @@
         <v>1.552631578947368</v>
       </c>
       <c r="H143" t="n">
-        <v>0.0001175912098807446</v>
+        <v>0.00160830371401117</v>
       </c>
     </row>
     <row r="144">
@@ -4757,7 +4757,7 @@
         <v>1.368421052631579</v>
       </c>
       <c r="H144" t="n">
-        <v>0.003420513327222125</v>
+        <v>0.02797871075139032</v>
       </c>
     </row>
     <row r="145">
@@ -4787,7 +4787,7 @@
         <v>0.9736842105263158</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1498118573448121</v>
+        <v>0.4329335739805773</v>
       </c>
     </row>
     <row r="146">
@@ -4817,7 +4817,7 @@
         <v>0.7368421052631579</v>
       </c>
       <c r="H146" t="n">
-        <v>0.8516234973428531</v>
+        <v>0.01469836502734483</v>
       </c>
     </row>
     <row r="147">
@@ -4847,7 +4847,7 @@
         <v>1.684210526315789</v>
       </c>
       <c r="H147" t="n">
-        <v>0.8932635901669871</v>
+        <v>0.7276528578134552</v>
       </c>
     </row>
     <row r="148">
@@ -4877,7 +4877,7 @@
         <v>1.947368421052632</v>
       </c>
       <c r="H148" t="n">
-        <v>0.3197303275428336</v>
+        <v>0.2024433959359452</v>
       </c>
     </row>
     <row r="149">
@@ -4907,7 +4907,7 @@
         <v>1.078947368421053</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1969254574728464</v>
+        <v>0.5463963149604113</v>
       </c>
     </row>
     <row r="150">
@@ -4937,7 +4937,7 @@
         <v>0.8947368421052632</v>
       </c>
       <c r="H150" t="n">
-        <v>0.765409872500734</v>
+        <v>0.3956855043936104</v>
       </c>
     </row>
     <row r="151">
@@ -4967,7 +4967,7 @@
         <v>1.631578947368421</v>
       </c>
       <c r="H151" t="n">
-        <v>3.314925224301662e-05</v>
+        <v>1.352776404557401e-05</v>
       </c>
     </row>
     <row r="152">
@@ -4997,7 +4997,7 @@
         <v>1.789473684210526</v>
       </c>
       <c r="H152" t="n">
-        <v>0.9994186540728106</v>
+        <v>0.9995611823832617</v>
       </c>
     </row>
     <row r="153">
@@ -5027,7 +5027,7 @@
         <v>0.9473684210526316</v>
       </c>
       <c r="H153" t="n">
-        <v>0.9984517687239161</v>
+        <v>0.9645683465051269</v>
       </c>
     </row>
     <row r="154">
@@ -5057,7 +5057,7 @@
         <v>1.868421052631579</v>
       </c>
       <c r="H154" t="n">
-        <v>0.9948852747809691</v>
+        <v>0.991013140587682</v>
       </c>
     </row>
     <row r="155">
@@ -5087,7 +5087,7 @@
         <v>2.5</v>
       </c>
       <c r="H155" t="n">
-        <v>0.001581899332098041</v>
+        <v>0.0001851897624866535</v>
       </c>
     </row>
     <row r="156">
@@ -5117,7 +5117,7 @@
         <v>0.5789473684210527</v>
       </c>
       <c r="H156" t="n">
-        <v>0.01325634256190074</v>
+        <v>0.01674286629199887</v>
       </c>
     </row>
     <row r="157">
@@ -5147,7 +5147,7 @@
         <v>1.184210526315789</v>
       </c>
       <c r="H157" t="n">
-        <v>0.004192988915706693</v>
+        <v>0.007667945070628459</v>
       </c>
     </row>
     <row r="158">
@@ -5177,7 +5177,7 @@
         <v>8.631578947368421</v>
       </c>
       <c r="H158" t="n">
-        <v>0.6531732517082942</v>
+        <v>0.652100976882119</v>
       </c>
     </row>
     <row r="159">
@@ -5207,7 +5207,7 @@
         <v>0.7894736842105263</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0003141949907584798</v>
+        <v>0.0001998147646089859</v>
       </c>
     </row>
     <row r="160">
@@ -5237,7 +5237,7 @@
         <v>54.6578947368421</v>
       </c>
       <c r="H160" t="n">
-        <v>0.0001723753818051357</v>
+        <v>0.0002220077243088309</v>
       </c>
     </row>
     <row r="161">
@@ -5267,7 +5267,7 @@
         <v>1.578947368421053</v>
       </c>
       <c r="H161" t="n">
-        <v>0.964206507147137</v>
+        <v>0.974242531563013</v>
       </c>
     </row>
     <row r="162">
@@ -5297,7 +5297,7 @@
         <v>4.789473684210527</v>
       </c>
       <c r="H162" t="n">
-        <v>0.01471949815374634</v>
+        <v>0.01022822434019471</v>
       </c>
     </row>
     <row r="163">
@@ -5327,7 +5327,7 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="H163" t="n">
-        <v>0.9645128981555596</v>
+        <v>0.9438738050782456</v>
       </c>
     </row>
     <row r="164">
@@ -5357,7 +5357,7 @@
         <v>5.315789473684211</v>
       </c>
       <c r="H164" t="n">
-        <v>0.9392161158027411</v>
+        <v>0.9434364736398754</v>
       </c>
     </row>
     <row r="165">
@@ -5387,7 +5387,7 @@
         <v>41.21052631578947</v>
       </c>
       <c r="H165" t="n">
-        <v>0.9999865290814257</v>
+        <v>0.9999876990458608</v>
       </c>
     </row>
     <row r="166">
@@ -5417,7 +5417,7 @@
         <v>5.289473684210527</v>
       </c>
       <c r="H166" t="n">
-        <v>7.820543331210262e-05</v>
+        <v>9.8499026572688e-05</v>
       </c>
     </row>
     <row r="167">
@@ -5447,7 +5447,7 @@
         <v>9</v>
       </c>
       <c r="H167" t="n">
-        <v>0.9940698519808727</v>
+        <v>0.9911687389049572</v>
       </c>
     </row>
     <row r="168">
@@ -5477,7 +5477,7 @@
         <v>3.5</v>
       </c>
       <c r="H168" t="n">
-        <v>0.9597706635095441</v>
+        <v>0.9611149715314558</v>
       </c>
     </row>
     <row r="169">
@@ -5507,7 +5507,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H169" t="n">
-        <v>0.02604039873597162</v>
+        <v>0.007595433229853512</v>
       </c>
     </row>
     <row r="170">
@@ -5537,7 +5537,7 @@
         <v>15.05263157894737</v>
       </c>
       <c r="H170" t="n">
-        <v>0.7188037025275775</v>
+        <v>0.7348254525031016</v>
       </c>
     </row>
     <row r="171">
@@ -5567,7 +5567,7 @@
         <v>8.631578947368421</v>
       </c>
       <c r="H171" t="n">
-        <v>0.9975516631788602</v>
+        <v>0.9982229770949693</v>
       </c>
     </row>
     <row r="172">
@@ -5597,7 +5597,7 @@
         <v>0.2631578947368421</v>
       </c>
       <c r="H172" t="n">
-        <v>0.9931902046157918</v>
+        <v>0.9951999153268831</v>
       </c>
     </row>
     <row r="173">
@@ -5627,7 +5627,7 @@
         <v>0.4736842105263157</v>
       </c>
       <c r="H173" t="n">
-        <v>0.9999765316902463</v>
+        <v>0.9999281771185669</v>
       </c>
     </row>
     <row r="174">
@@ -5657,7 +5657,7 @@
         <v>1.684210526315789</v>
       </c>
       <c r="H174" t="n">
-        <v>0.03951296285149158</v>
+        <v>0.006028178883417144</v>
       </c>
     </row>
     <row r="175">
@@ -5687,7 +5687,7 @@
         <v>7.710526315789473</v>
       </c>
       <c r="H175" t="n">
-        <v>0.001780373386066523</v>
+        <v>0.002409319890755737</v>
       </c>
     </row>
     <row r="176">
@@ -5717,7 +5717,7 @@
         <v>0.4473684210526316</v>
       </c>
       <c r="H176" t="n">
-        <v>0.9995266984736728</v>
+        <v>0.9997940485365454</v>
       </c>
     </row>
     <row r="177">
@@ -5747,7 +5747,7 @@
         <v>55.71052631578947</v>
       </c>
       <c r="H177" t="n">
-        <v>0.4501927303854099</v>
+        <v>0.4516439578738764</v>
       </c>
     </row>
     <row r="178">
@@ -5777,7 +5777,7 @@
         <v>7.342105263157895</v>
       </c>
       <c r="H178" t="n">
-        <v>0.9191932752875892</v>
+        <v>0.9651774004632697</v>
       </c>
     </row>
     <row r="179">
@@ -5807,7 +5807,7 @@
         <v>17.07894736842105</v>
       </c>
       <c r="H179" t="n">
-        <v>0.009538825432062109</v>
+        <v>0.009943057342922815</v>
       </c>
     </row>
     <row r="180">
@@ -5837,7 +5837,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H180" t="n">
-        <v>0.0472152108968003</v>
+        <v>0.06077033396968139</v>
       </c>
     </row>
     <row r="181">
@@ -5867,7 +5867,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H181" t="n">
-        <v>0.9608870264844994</v>
+        <v>0.9439351035141091</v>
       </c>
     </row>
     <row r="182">
@@ -5897,7 +5897,7 @@
         <v>17.40223463687151</v>
       </c>
       <c r="H182" t="n">
-        <v>0.9955680176581165</v>
+        <v>0.9965604757144318</v>
       </c>
     </row>
     <row r="183">
@@ -5927,7 +5927,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H183" t="n">
-        <v>0.9901752336806355</v>
+        <v>0.9922059400606984</v>
       </c>
     </row>
     <row r="184">
@@ -5957,7 +5957,7 @@
         <v>7.178770949720671</v>
       </c>
       <c r="H184" t="n">
-        <v>0.09913909074671316</v>
+        <v>0.09877344183810859</v>
       </c>
     </row>
     <row r="185">
@@ -5987,7 +5987,7 @@
         <v>7.011173184357543</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1905937445252861</v>
+        <v>0.1824681577421172</v>
       </c>
     </row>
     <row r="186">
@@ -6017,7 +6017,7 @@
         <v>11.95530726256983</v>
       </c>
       <c r="H186" t="n">
-        <v>0.003603896714005455</v>
+        <v>0.002977566141044414</v>
       </c>
     </row>
     <row r="187">
@@ -6047,7 +6047,7 @@
         <v>0.6983240223463688</v>
       </c>
       <c r="H187" t="n">
-        <v>0.9959002932947039</v>
+        <v>0.9935914565695958</v>
       </c>
     </row>
     <row r="188">
@@ -6077,7 +6077,7 @@
         <v>46.08938547486034</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9906086449638009</v>
+        <v>0.9914752443517959</v>
       </c>
     </row>
     <row r="189">
@@ -6107,7 +6107,7 @@
         <v>2.067039106145252</v>
       </c>
       <c r="H189" t="n">
-        <v>0.00147048177718415</v>
+        <v>0.001386620534155587</v>
       </c>
     </row>
     <row r="190">
@@ -6137,7 +6137,7 @@
         <v>35.81005586592179</v>
       </c>
       <c r="H190" t="n">
-        <v>0.9992002156560343</v>
+        <v>0.998074425718643</v>
       </c>
     </row>
     <row r="191">
@@ -6167,7 +6167,7 @@
         <v>7.178770949720671</v>
       </c>
       <c r="H191" t="n">
-        <v>0.0706920845218959</v>
+        <v>0.06119164723020958</v>
       </c>
     </row>
     <row r="192">
@@ -6197,7 +6197,7 @@
         <v>6.843575418994414</v>
       </c>
       <c r="H192" t="n">
-        <v>0.9983656038577026</v>
+        <v>0.9976163381934688</v>
       </c>
     </row>
     <row r="193">
@@ -6227,7 +6227,7 @@
         <v>1.871508379888268</v>
       </c>
       <c r="H193" t="n">
-        <v>0.03745393114484459</v>
+        <v>0.03676530384028599</v>
       </c>
     </row>
     <row r="194">
@@ -6257,7 +6257,7 @@
         <v>18</v>
       </c>
       <c r="H194" t="n">
-        <v>0.01042663319355623</v>
+        <v>0.000753351817322322</v>
       </c>
     </row>
     <row r="195">
@@ -6287,7 +6287,7 @@
         <v>8</v>
       </c>
       <c r="H195" t="n">
-        <v>0.9201050246357332</v>
+        <v>0.231391409351942</v>
       </c>
     </row>
     <row r="196">
@@ -6317,7 +6317,7 @@
         <v>18</v>
       </c>
       <c r="H196" t="n">
-        <v>0.432286577187356</v>
+        <v>0.01190486884718608</v>
       </c>
     </row>
     <row r="197">
@@ -6347,7 +6347,7 @@
         <v>2</v>
       </c>
       <c r="H197" t="n">
-        <v>0.0002041492873018957</v>
+        <v>1.029358209708813e-06</v>
       </c>
     </row>
     <row r="198">
@@ -6377,7 +6377,7 @@
         <v>8</v>
       </c>
       <c r="H198" t="n">
-        <v>0.0859216192635472</v>
+        <v>0.001610740902210828</v>
       </c>
     </row>
     <row r="199">
@@ -6407,7 +6407,7 @@
         <v>9</v>
       </c>
       <c r="H199" t="n">
-        <v>0.1663239771843768</v>
+        <v>0.01487979158658972</v>
       </c>
     </row>
     <row r="200">
@@ -6437,7 +6437,7 @@
         <v>21</v>
       </c>
       <c r="H200" t="n">
-        <v>0.07980466438903243</v>
+        <v>0.1083529871180596</v>
       </c>
     </row>
     <row r="201">
@@ -6467,7 +6467,7 @@
         <v>8</v>
       </c>
       <c r="H201" t="n">
-        <v>6.878296581222518e-05</v>
+        <v>6.098178718712074e-09</v>
       </c>
     </row>
     <row r="202">
@@ -6497,7 +6497,7 @@
         <v>5</v>
       </c>
       <c r="H202" t="n">
-        <v>0.001186848750443481</v>
+        <v>7.302646936685163e-05</v>
       </c>
     </row>
     <row r="203">
@@ -6527,7 +6527,7 @@
         <v>8</v>
       </c>
       <c r="H203" t="n">
-        <v>0.000701089585755532</v>
+        <v>0.0009982230823907766</v>
       </c>
     </row>
     <row r="204">
@@ -6557,7 +6557,7 @@
         <v>2</v>
       </c>
       <c r="H204" t="n">
-        <v>0.4597395671304257</v>
+        <v>0.006488621213181343</v>
       </c>
     </row>
     <row r="205">
@@ -6587,7 +6587,7 @@
         <v>20</v>
       </c>
       <c r="H205" t="n">
-        <v>0.679258843496738</v>
+        <v>0.9819488276927527</v>
       </c>
     </row>
     <row r="206">
@@ -6617,7 +6617,7 @@
         <v>5</v>
       </c>
       <c r="H206" t="n">
-        <v>0.002729679222721144</v>
+        <v>2.324799426605524e-06</v>
       </c>
     </row>
     <row r="207">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="H207" t="n">
-        <v>0.9850862981433223</v>
+        <v>0.0926130023506416</v>
       </c>
     </row>
     <row r="208">
@@ -6677,7 +6677,7 @@
         <v>1</v>
       </c>
       <c r="H208" t="n">
-        <v>0.2414862766214311</v>
+        <v>0.0001513400971954038</v>
       </c>
     </row>
     <row r="209">
@@ -6707,7 +6707,7 @@
         <v>8</v>
       </c>
       <c r="H209" t="n">
-        <v>1.783492594639839e-06</v>
+        <v>2.382324112784011e-07</v>
       </c>
     </row>
     <row r="210">
@@ -6737,7 +6737,7 @@
         <v>13</v>
       </c>
       <c r="H210" t="n">
-        <v>0.002844400843604094</v>
+        <v>0.03380200182254701</v>
       </c>
     </row>
     <row r="211">
@@ -6767,7 +6767,7 @@
         <v>2</v>
       </c>
       <c r="H211" t="n">
-        <v>0.09190207134798972</v>
+        <v>0.3452811822892862</v>
       </c>
     </row>
     <row r="212">
@@ -6797,7 +6797,7 @@
         <v>7</v>
       </c>
       <c r="H212" t="n">
-        <v>0.1059638989205033</v>
+        <v>5.283412334120213e-05</v>
       </c>
     </row>
     <row r="213">
@@ -6827,7 +6827,7 @@
         <v>7</v>
       </c>
       <c r="H213" t="n">
-        <v>2.020844526984385e-05</v>
+        <v>0.0004222784298100751</v>
       </c>
     </row>
     <row r="214">
@@ -6857,7 +6857,7 @@
         <v>2</v>
       </c>
       <c r="H214" t="n">
-        <v>3.676255539096824e-05</v>
+        <v>0.0002673261737637341</v>
       </c>
     </row>
     <row r="215">
@@ -6887,7 +6887,7 @@
         <v>8</v>
       </c>
       <c r="H215" t="n">
-        <v>0.0001758833956213105</v>
+        <v>3.772157640668125e-05</v>
       </c>
     </row>
     <row r="216">
@@ -6917,7 +6917,7 @@
         <v>6</v>
       </c>
       <c r="H216" t="n">
-        <v>1.036262328485313e-05</v>
+        <v>3.244762027968647e-06</v>
       </c>
     </row>
     <row r="217">
@@ -6947,7 +6947,7 @@
         <v>8</v>
       </c>
       <c r="H217" t="n">
-        <v>1.572116110916982e-05</v>
+        <v>0.1283084710574066</v>
       </c>
     </row>
     <row r="218">
@@ -6977,7 +6977,7 @@
         <v>8</v>
       </c>
       <c r="H218" t="n">
-        <v>1.327139403372115e-05</v>
+        <v>2.939540685014896e-05</v>
       </c>
     </row>
     <row r="219">
@@ -7007,7 +7007,7 @@
         <v>8</v>
       </c>
       <c r="H219" t="n">
-        <v>8.203782817326743e-05</v>
+        <v>0.002151963980599278</v>
       </c>
     </row>
     <row r="220">
@@ -7037,7 +7037,7 @@
         <v>14</v>
       </c>
       <c r="H220" t="n">
-        <v>2.349176313574837e-08</v>
+        <v>5.035744231907016e-07</v>
       </c>
     </row>
     <row r="221">
@@ -7067,7 +7067,7 @@
         <v>5</v>
       </c>
       <c r="H221" t="n">
-        <v>0.02457669907045262</v>
+        <v>0.2238103871283354</v>
       </c>
     </row>
     <row r="222">
@@ -7097,7 +7097,7 @@
         <v>20</v>
       </c>
       <c r="H222" t="n">
-        <v>2.889425346261243e-05</v>
+        <v>7.83789223660781e-05</v>
       </c>
     </row>
     <row r="223">
@@ -7127,7 +7127,7 @@
         <v>3</v>
       </c>
       <c r="H223" t="n">
-        <v>0.001433191536138224</v>
+        <v>0.001004151696298988</v>
       </c>
     </row>
     <row r="224">
@@ -7157,7 +7157,7 @@
         <v>8</v>
       </c>
       <c r="H224" t="n">
-        <v>0.003017073709052633</v>
+        <v>0.1378619523597674</v>
       </c>
     </row>
     <row r="225">
@@ -7187,7 +7187,7 @@
         <v>17</v>
       </c>
       <c r="H225" t="n">
-        <v>0.001044938019468717</v>
+        <v>0.8657345199975579</v>
       </c>
     </row>
     <row r="226">
@@ -7217,7 +7217,7 @@
         <v>12</v>
       </c>
       <c r="H226" t="n">
-        <v>0.0008496538871504174</v>
+        <v>0.1732210894058257</v>
       </c>
     </row>
     <row r="227">
@@ -7247,7 +7247,7 @@
         <v>5</v>
       </c>
       <c r="H227" t="n">
-        <v>0.00817254311844326</v>
+        <v>0.754080220660743</v>
       </c>
     </row>
     <row r="228">
@@ -7277,7 +7277,7 @@
         <v>7</v>
       </c>
       <c r="H228" t="n">
-        <v>0.0006093906887942145</v>
+        <v>0.3501600046769842</v>
       </c>
     </row>
     <row r="229">
@@ -7307,7 +7307,7 @@
         <v>14</v>
       </c>
       <c r="H229" t="n">
-        <v>0.6965446511174482</v>
+        <v>0.6027561619109081</v>
       </c>
     </row>
     <row r="230">
@@ -7337,7 +7337,7 @@
         <v>12</v>
       </c>
       <c r="H230" t="n">
-        <v>0.01397232879165014</v>
+        <v>0.02850488095716764</v>
       </c>
     </row>
     <row r="231">
@@ -7367,7 +7367,7 @@
         <v>8</v>
       </c>
       <c r="H231" t="n">
-        <v>0.5948290645899346</v>
+        <v>0.9987517601038793</v>
       </c>
     </row>
     <row r="232">
@@ -7397,7 +7397,7 @@
         <v>4</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1597647185233794</v>
+        <v>0.7264156443895383</v>
       </c>
     </row>
     <row r="233">
@@ -7427,7 +7427,7 @@
         <v>6</v>
       </c>
       <c r="H233" t="n">
-        <v>0.02523394957185481</v>
+        <v>6.680450792250216e-05</v>
       </c>
     </row>
     <row r="234">
@@ -7457,7 +7457,7 @@
         <v>18</v>
       </c>
       <c r="H234" t="n">
-        <v>0.02843408405293641</v>
+        <v>0.4763561213132422</v>
       </c>
     </row>
     <row r="235">
@@ -7487,7 +7487,7 @@
         <v>8</v>
       </c>
       <c r="H235" t="n">
-        <v>0.0001432038919115088</v>
+        <v>0.0009121213917631862</v>
       </c>
     </row>
     <row r="236">
@@ -7517,7 +7517,7 @@
         <v>18</v>
       </c>
       <c r="H236" t="n">
-        <v>0.007623501166692648</v>
+        <v>0.001118708863491905</v>
       </c>
     </row>
     <row r="237">
@@ -7547,7 +7547,7 @@
         <v>35</v>
       </c>
       <c r="H237" t="n">
-        <v>0.9999907980571996</v>
+        <v>0.9989146456058486</v>
       </c>
     </row>
     <row r="238">
@@ -7577,7 +7577,7 @@
         <v>5</v>
       </c>
       <c r="H238" t="n">
-        <v>4.286108929410578e-05</v>
+        <v>0.001080665474368858</v>
       </c>
     </row>
     <row r="239">
@@ -7607,7 +7607,7 @@
         <v>3</v>
       </c>
       <c r="H239" t="n">
-        <v>0.05428062925589951</v>
+        <v>0.001161832137679517</v>
       </c>
     </row>
     <row r="240">
@@ -7637,7 +7637,7 @@
         <v>22</v>
       </c>
       <c r="H240" t="n">
-        <v>0.4884016958764351</v>
+        <v>0.08381063385630713</v>
       </c>
     </row>
     <row r="241">
@@ -7667,7 +7667,7 @@
         <v>8</v>
       </c>
       <c r="H241" t="n">
-        <v>6.954777034065141e-06</v>
+        <v>0.0001063879274465712</v>
       </c>
     </row>
     <row r="242">
@@ -7697,7 +7697,7 @@
         <v>15</v>
       </c>
       <c r="H242" t="n">
-        <v>0.01014716894199839</v>
+        <v>0.02403711709021166</v>
       </c>
     </row>
     <row r="243">
@@ -7727,7 +7727,7 @@
         <v>14</v>
       </c>
       <c r="H243" t="n">
-        <v>0.08752951442084211</v>
+        <v>5.730796127967742e-06</v>
       </c>
     </row>
     <row r="244">
@@ -7757,7 +7757,7 @@
         <v>10</v>
       </c>
       <c r="H244" t="n">
-        <v>1.968477392937448e-05</v>
+        <v>5.219970747973038e-05</v>
       </c>
     </row>
     <row r="245">
@@ -7787,7 +7787,7 @@
         <v>14</v>
       </c>
       <c r="H245" t="n">
-        <v>0.6827922805721299</v>
+        <v>0.343156030563777</v>
       </c>
     </row>
     <row r="246">
@@ -7817,7 +7817,7 @@
         <v>17</v>
       </c>
       <c r="H246" t="n">
-        <v>0.03311592024459931</v>
+        <v>0.7245742995439546</v>
       </c>
     </row>
     <row r="247">
@@ -7847,7 +7847,7 @@
         <v>6</v>
       </c>
       <c r="H247" t="n">
-        <v>8.39589970061279e-06</v>
+        <v>0.0001109226862875412</v>
       </c>
     </row>
     <row r="248">
@@ -7877,7 +7877,7 @@
         <v>9</v>
       </c>
       <c r="H248" t="n">
-        <v>0.0001555654627226193</v>
+        <v>0.1927092997053424</v>
       </c>
     </row>
     <row r="249">
@@ -7907,7 +7907,7 @@
         <v>8</v>
       </c>
       <c r="H249" t="n">
-        <v>0.2230713089202576</v>
+        <v>0.1146719951371492</v>
       </c>
     </row>
     <row r="250">
@@ -7937,7 +7937,7 @@
         <v>8</v>
       </c>
       <c r="H250" t="n">
-        <v>6.266613313540369e-05</v>
+        <v>0.0006543910020356087</v>
       </c>
     </row>
     <row r="251">
@@ -7967,7 +7967,7 @@
         <v>1</v>
       </c>
       <c r="H251" t="n">
-        <v>4.214964063308397e-05</v>
+        <v>6.353920649866036e-05</v>
       </c>
     </row>
     <row r="252">
@@ -7997,7 +7997,7 @@
         <v>7</v>
       </c>
       <c r="H252" t="n">
-        <v>0.1665711404980328</v>
+        <v>0.9762039232820267</v>
       </c>
     </row>
     <row r="253">
@@ -8027,7 +8027,7 @@
         <v>7</v>
       </c>
       <c r="H253" t="n">
-        <v>0.0300586997304185</v>
+        <v>0.09899544343799324</v>
       </c>
     </row>
     <row r="254">
@@ -8057,7 +8057,7 @@
         <v>1.368421052631579</v>
       </c>
       <c r="H254" t="n">
-        <v>0.96381489811119</v>
+        <v>0.9998868092019032</v>
       </c>
     </row>
     <row r="255">
@@ -8087,7 +8087,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H255" t="n">
-        <v>0.4876059522056574</v>
+        <v>0.921292977796902</v>
       </c>
     </row>
     <row r="256">
@@ -8117,7 +8117,7 @@
         <v>0.5263157894736842</v>
       </c>
       <c r="H256" t="n">
-        <v>7.414269232060151e-08</v>
+        <v>1.647960163573019e-08</v>
       </c>
     </row>
     <row r="257">
@@ -8147,7 +8147,7 @@
         <v>1.184210526315789</v>
       </c>
       <c r="H257" t="n">
-        <v>0.9999528697905167</v>
+        <v>0.9994724364725172</v>
       </c>
     </row>
     <row r="258">
@@ -8177,7 +8177,7 @@
         <v>1.210526315789474</v>
       </c>
       <c r="H258" t="n">
-        <v>0.01002316585174864</v>
+        <v>9.048085081931455e-06</v>
       </c>
     </row>
     <row r="259">
@@ -8207,7 +8207,7 @@
         <v>0.9210526315789472</v>
       </c>
       <c r="H259" t="n">
-        <v>0.00400506087741056</v>
+        <v>0.07014052593079549</v>
       </c>
     </row>
     <row r="260">
@@ -8237,7 +8237,7 @@
         <v>1.921052631578948</v>
       </c>
       <c r="H260" t="n">
-        <v>5.151164727826551e-05</v>
+        <v>4.636294287488628e-05</v>
       </c>
     </row>
     <row r="261">
@@ -8267,7 +8267,7 @@
         <v>3.684210526315789</v>
       </c>
       <c r="H261" t="n">
-        <v>0.9997768307884323</v>
+        <v>0.8095948553549335</v>
       </c>
     </row>
     <row r="262">
@@ -8297,7 +8297,7 @@
         <v>1.789473684210526</v>
       </c>
       <c r="H262" t="n">
-        <v>0.9769692234657839</v>
+        <v>0.6979846232291828</v>
       </c>
     </row>
     <row r="263">
@@ -8327,7 +8327,7 @@
         <v>3.105263157894737</v>
       </c>
       <c r="H263" t="n">
-        <v>0.005784154509080609</v>
+        <v>0.1562589412860037</v>
       </c>
     </row>
     <row r="264">
@@ -8357,7 +8357,7 @@
         <v>1.342105263157895</v>
       </c>
       <c r="H264" t="n">
-        <v>0.05160086618302089</v>
+        <v>0.8740429229267542</v>
       </c>
     </row>
     <row r="265">
@@ -8387,7 +8387,7 @@
         <v>1.605263157894737</v>
       </c>
       <c r="H265" t="n">
-        <v>0.7744521800690082</v>
+        <v>0.5152873178960667</v>
       </c>
     </row>
     <row r="266">
@@ -8417,7 +8417,7 @@
         <v>2.368421052631579</v>
       </c>
       <c r="H266" t="n">
-        <v>0.9412104065839038</v>
+        <v>0.5042553919953304</v>
       </c>
     </row>
     <row r="267">
@@ -8447,7 +8447,7 @@
         <v>2.210526315789474</v>
       </c>
       <c r="H267" t="n">
-        <v>0.9558574414703433</v>
+        <v>0.1433035309116577</v>
       </c>
     </row>
     <row r="268">
@@ -8477,7 +8477,7 @@
         <v>4.078947368421052</v>
       </c>
       <c r="H268" t="n">
-        <v>0.001566161047042403</v>
+        <v>0.4796471754216041</v>
       </c>
     </row>
     <row r="269">
@@ -8507,7 +8507,7 @@
         <v>1.842105263157895</v>
       </c>
       <c r="H269" t="n">
-        <v>0.6134505966835033</v>
+        <v>0.3938949001735972</v>
       </c>
     </row>
     <row r="270">
@@ -8537,7 +8537,7 @@
         <v>1.131578947368421</v>
       </c>
       <c r="H270" t="n">
-        <v>0.2792696068631169</v>
+        <v>0.7256043588453642</v>
       </c>
     </row>
     <row r="271">
@@ -8567,7 +8567,7 @@
         <v>1.973684210526316</v>
       </c>
       <c r="H271" t="n">
-        <v>0.9977730756775085</v>
+        <v>0.05216727935149926</v>
       </c>
     </row>
     <row r="272">
@@ -8597,7 +8597,7 @@
         <v>0.5</v>
       </c>
       <c r="H272" t="n">
-        <v>7.670558412260169e-06</v>
+        <v>2.985789338242163e-07</v>
       </c>
     </row>
     <row r="273">
@@ -8627,7 +8627,7 @@
         <v>1.763157894736842</v>
       </c>
       <c r="H273" t="n">
-        <v>0.1173278387241181</v>
+        <v>0.3509711109260866</v>
       </c>
     </row>
     <row r="274">
@@ -8657,7 +8657,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="H274" t="n">
-        <v>0.001981103625044979</v>
+        <v>0.006599058794615502</v>
       </c>
     </row>
     <row r="275">
@@ -8687,7 +8687,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H275" t="n">
-        <v>0.04560594962482909</v>
+        <v>0.6612899486979023</v>
       </c>
     </row>
     <row r="276">
@@ -8717,7 +8717,7 @@
         <v>2.368421052631579</v>
       </c>
       <c r="H276" t="n">
-        <v>0.1927520216846918</v>
+        <v>0.4248865717602464</v>
       </c>
     </row>
     <row r="277">
@@ -8747,7 +8747,7 @@
         <v>2.710526315789474</v>
       </c>
       <c r="H277" t="n">
-        <v>0.001237269153620764</v>
+        <v>0.0005497359023346757</v>
       </c>
     </row>
     <row r="278">
@@ -8777,7 +8777,7 @@
         <v>1.868421052631579</v>
       </c>
       <c r="H278" t="n">
-        <v>0.3318005918564329</v>
+        <v>0.8542357953250362</v>
       </c>
     </row>
     <row r="279">
@@ -8807,7 +8807,7 @@
         <v>3.289473684210526</v>
       </c>
       <c r="H279" t="n">
-        <v>0.006185016954640745</v>
+        <v>0.00989132860185459</v>
       </c>
     </row>
     <row r="280">
@@ -8837,7 +8837,7 @@
         <v>3.947368421052632</v>
       </c>
       <c r="H280" t="n">
-        <v>0.02357364897797054</v>
+        <v>0.002187746666202054</v>
       </c>
     </row>
     <row r="281">
@@ -8867,7 +8867,7 @@
         <v>6.052631578947368</v>
       </c>
       <c r="H281" t="n">
-        <v>0.7731316563855564</v>
+        <v>0.7960929281132835</v>
       </c>
     </row>
     <row r="282">
@@ -8897,7 +8897,7 @@
         <v>20.18421052631579</v>
       </c>
       <c r="H282" t="n">
-        <v>0.8993341384826301</v>
+        <v>0.8717216920591621</v>
       </c>
     </row>
     <row r="283">
@@ -8927,7 +8927,7 @@
         <v>8.973684210526315</v>
       </c>
       <c r="H283" t="n">
-        <v>0.0003243195263369011</v>
+        <v>0.00024157756760196</v>
       </c>
     </row>
     <row r="284">
@@ -8957,7 +8957,7 @@
         <v>1.263157894736842</v>
       </c>
       <c r="H284" t="n">
-        <v>0.7761067385335871</v>
+        <v>0.6824669320966024</v>
       </c>
     </row>
     <row r="285">
@@ -8987,7 +8987,7 @@
         <v>8.421052631578947</v>
       </c>
       <c r="H285" t="n">
-        <v>0.2777300073088935</v>
+        <v>0.3938785449901512</v>
       </c>
     </row>
     <row r="286">
@@ -9017,7 +9017,7 @@
         <v>5.763157894736842</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1230023821416515</v>
+        <v>0.1163748702656302</v>
       </c>
     </row>
     <row r="287">
@@ -9047,7 +9047,7 @@
         <v>6.710526315789473</v>
       </c>
       <c r="H287" t="n">
-        <v>0.8354614268200671</v>
+        <v>0.8499214989762809</v>
       </c>
     </row>
     <row r="288">
@@ -9077,7 +9077,7 @@
         <v>1.105263157894737</v>
       </c>
       <c r="H288" t="n">
-        <v>0.8784671691728628</v>
+        <v>0.8458672436415159</v>
       </c>
     </row>
     <row r="289">
@@ -9107,7 +9107,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="H289" t="n">
-        <v>0.06491189410430981</v>
+        <v>0.06486805517119243</v>
       </c>
     </row>
     <row r="290">
@@ -9137,7 +9137,7 @@
         <v>36.36842105263158</v>
       </c>
       <c r="H290" t="n">
-        <v>0.9974796529446093</v>
+        <v>0.9948399779306497</v>
       </c>
     </row>
     <row r="291">
@@ -9167,7 +9167,7 @@
         <v>9.605263157894736</v>
       </c>
       <c r="H291" t="n">
-        <v>0.9910423409335287</v>
+        <v>0.9910019064370383</v>
       </c>
     </row>
     <row r="292">
@@ -9197,7 +9197,7 @@
         <v>7.236842105263157</v>
       </c>
       <c r="H292" t="n">
-        <v>0.03020064941888344</v>
+        <v>0.04493528447692999</v>
       </c>
     </row>
     <row r="293">
@@ -9227,7 +9227,7 @@
         <v>1.315789473684211</v>
       </c>
       <c r="H293" t="n">
-        <v>0.02493237299049457</v>
+        <v>0.04349444470185922</v>
       </c>
     </row>
     <row r="294">
@@ -9257,7 +9257,7 @@
         <v>51.6578947368421</v>
       </c>
       <c r="H294" t="n">
-        <v>0.9989309175089868</v>
+        <v>0.9991990381733591</v>
       </c>
     </row>
     <row r="295">
@@ -9287,7 +9287,7 @@
         <v>1.552631578947368</v>
       </c>
       <c r="H295" t="n">
-        <v>7.271264774139312e-05</v>
+        <v>6.453014925922857e-05</v>
       </c>
     </row>
     <row r="296">
@@ -9317,7 +9317,7 @@
         <v>142.7894736842105</v>
       </c>
       <c r="H296" t="n">
-        <v>0.9999999998288613</v>
+        <v>0.9999999988128581</v>
       </c>
     </row>
     <row r="297">
@@ -9347,7 +9347,7 @@
         <v>4.157894736842105</v>
       </c>
       <c r="H297" t="n">
-        <v>0.3834711969555186</v>
+        <v>0.4995845267259685</v>
       </c>
     </row>
     <row r="298">
@@ -9377,7 +9377,7 @@
         <v>7.105263157894737</v>
       </c>
       <c r="H298" t="n">
-        <v>0.0699267710660836</v>
+        <v>0.0930752456622977</v>
       </c>
     </row>
     <row r="299">
@@ -9407,7 +9407,7 @@
         <v>1.052631578947368</v>
       </c>
       <c r="H299" t="n">
-        <v>0.8059398909081568</v>
+        <v>0.7775064408182714</v>
       </c>
     </row>
     <row r="300">
@@ -9437,7 +9437,7 @@
         <v>4.736842105263158</v>
       </c>
       <c r="H300" t="n">
-        <v>0.003506512904212763</v>
+        <v>0.003700297509797714</v>
       </c>
     </row>
     <row r="301">
@@ -9467,7 +9467,7 @@
         <v>160.6052631578947</v>
       </c>
       <c r="H301" t="n">
-        <v>0.01934548837164289</v>
+        <v>0.08742475653823598</v>
       </c>
     </row>
     <row r="302">
@@ -9497,7 +9497,7 @@
         <v>13.3421052631579</v>
       </c>
       <c r="H302" t="n">
-        <v>0.9372080417555193</v>
+        <v>0.9430122384033518</v>
       </c>
     </row>
     <row r="303">
@@ -9527,7 +9527,7 @@
         <v>19.89473684210526</v>
       </c>
       <c r="H303" t="n">
-        <v>0.7598424467207484</v>
+        <v>0.8330830542199951</v>
       </c>
     </row>
     <row r="304">
@@ -9557,7 +9557,7 @@
         <v>24.60526315789474</v>
       </c>
       <c r="H304" t="n">
-        <v>0.5279725579344307</v>
+        <v>0.1457170770468946</v>
       </c>
     </row>
     <row r="305">
@@ -9587,7 +9587,7 @@
         <v>5.394736842105263</v>
       </c>
       <c r="H305" t="n">
-        <v>0.0002496714958419465</v>
+        <v>0.0004814467061000808</v>
       </c>
     </row>
     <row r="306">
@@ -9617,7 +9617,7 @@
         <v>8.268156424581006</v>
       </c>
       <c r="H306" t="n">
-        <v>0.06150653178473513</v>
+        <v>0.1968351807911424</v>
       </c>
     </row>
     <row r="307">
@@ -9647,7 +9647,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H307" t="n">
-        <v>0.3210813123788929</v>
+        <v>0.08606164034729898</v>
       </c>
     </row>
     <row r="308">
@@ -9677,7 +9677,7 @@
         <v>25.3072625698324</v>
       </c>
       <c r="H308" t="n">
-        <v>0.9999926873634231</v>
+        <v>0.9999981216401821</v>
       </c>
     </row>
     <row r="309">
@@ -9707,7 +9707,7 @@
         <v>6.703910614525141</v>
       </c>
       <c r="H309" t="n">
-        <v>0.5783877694586524</v>
+        <v>0.8892240045180315</v>
       </c>
     </row>
     <row r="310">
@@ -9737,7 +9737,7 @@
         <v>2.905027932960894</v>
       </c>
       <c r="H310" t="n">
-        <v>0.5228491076530716</v>
+        <v>0.662743225368684</v>
       </c>
     </row>
     <row r="311">
@@ -9767,7 +9767,7 @@
         <v>3.519553072625698</v>
       </c>
       <c r="H311" t="n">
-        <v>0.9714540514128334</v>
+        <v>0.9703413483077561</v>
       </c>
     </row>
     <row r="312">
@@ -9797,7 +9797,7 @@
         <v>11.42458100558659</v>
       </c>
       <c r="H312" t="n">
-        <v>0.9996103538531332</v>
+        <v>0.9999312409402694</v>
       </c>
     </row>
     <row r="313">
@@ -9827,7 +9827,7 @@
         <v>82.37430167597766</v>
       </c>
       <c r="H313" t="n">
-        <v>0.1827905446771031</v>
+        <v>0.1221598363267111</v>
       </c>
     </row>
     <row r="314">
@@ -9857,7 +9857,7 @@
         <v>4.050279329608939</v>
       </c>
       <c r="H314" t="n">
-        <v>0.6165174254021524</v>
+        <v>0.622146631759688</v>
       </c>
     </row>
     <row r="315">
@@ -9887,7 +9887,7 @@
         <v>9.553072625698324</v>
       </c>
       <c r="H315" t="n">
-        <v>0.5363388093212674</v>
+        <v>0.619562143731242</v>
       </c>
     </row>
     <row r="316">
@@ -9917,7 +9917,7 @@
         <v>7.29050279329609</v>
       </c>
       <c r="H316" t="n">
-        <v>0.5314975325187653</v>
+        <v>0.6204042739382061</v>
       </c>
     </row>
     <row r="317">
@@ -9947,7 +9947,7 @@
         <v>18.77094972067039</v>
       </c>
       <c r="H317" t="n">
-        <v>0.9992715730082561</v>
+        <v>0.9993387765947258</v>
       </c>
     </row>
     <row r="318">
@@ -9977,7 +9977,7 @@
         <v>1.983240223463687</v>
       </c>
       <c r="H318" t="n">
-        <v>0.01393423711112059</v>
+        <v>0.02784324476783885</v>
       </c>
     </row>
     <row r="319">
@@ -10007,7 +10007,7 @@
         <v>17.93296089385475</v>
       </c>
       <c r="H319" t="n">
-        <v>0.9231334609328685</v>
+        <v>0.7594871714433515</v>
       </c>
     </row>
     <row r="320">
@@ -10037,7 +10037,7 @@
         <v>1</v>
       </c>
       <c r="H320" t="n">
-        <v>0.001126308403544105</v>
+        <v>8.20405705212778e-05</v>
       </c>
     </row>
     <row r="321">
@@ -10067,7 +10067,7 @@
         <v>2</v>
       </c>
       <c r="H321" t="n">
-        <v>0.00355128606178819</v>
+        <v>0.03486466159976914</v>
       </c>
     </row>
     <row r="322">
@@ -10097,7 +10097,7 @@
         <v>11</v>
       </c>
       <c r="H322" t="n">
-        <v>0.5828958205449618</v>
+        <v>0.004547736256832461</v>
       </c>
     </row>
     <row r="323">
@@ -10127,7 +10127,7 @@
         <v>4</v>
       </c>
       <c r="H323" t="n">
-        <v>0.001443274987033947</v>
+        <v>3.393441736718447e-05</v>
       </c>
     </row>
     <row r="324">
@@ -10157,7 +10157,7 @@
         <v>8</v>
       </c>
       <c r="H324" t="n">
-        <v>0.04978430448145773</v>
+        <v>2.006186084132305e-05</v>
       </c>
     </row>
     <row r="325">
@@ -10187,7 +10187,7 @@
         <v>38</v>
       </c>
       <c r="H325" t="n">
-        <v>0.3466477306778675</v>
+        <v>0.2511703695333304</v>
       </c>
     </row>
     <row r="326">
@@ -10217,7 +10217,7 @@
         <v>6</v>
       </c>
       <c r="H326" t="n">
-        <v>6.641088399644122e-06</v>
+        <v>4.14683853209416e-05</v>
       </c>
     </row>
     <row r="327">
@@ -10247,7 +10247,7 @@
         <v>11</v>
       </c>
       <c r="H327" t="n">
-        <v>0.0005096517811776171</v>
+        <v>0.06182505942868818</v>
       </c>
     </row>
     <row r="328">
@@ -10277,7 +10277,7 @@
         <v>8</v>
       </c>
       <c r="H328" t="n">
-        <v>7.447481699426436e-05</v>
+        <v>0.0004219658999854101</v>
       </c>
     </row>
     <row r="329">
@@ -10307,7 +10307,7 @@
         <v>6</v>
       </c>
       <c r="H329" t="n">
-        <v>0.00534782691397834</v>
+        <v>0.001142894369652539</v>
       </c>
     </row>
     <row r="330">
@@ -10337,7 +10337,7 @@
         <v>12</v>
       </c>
       <c r="H330" t="n">
-        <v>0.942594266025149</v>
+        <v>0.5246758768235007</v>
       </c>
     </row>
     <row r="331">
@@ -10367,7 +10367,7 @@
         <v>11</v>
       </c>
       <c r="H331" t="n">
-        <v>0.08476580118866819</v>
+        <v>0.0008475701210377812</v>
       </c>
     </row>
     <row r="332">
@@ -10397,7 +10397,7 @@
         <v>5</v>
       </c>
       <c r="H332" t="n">
-        <v>0.0001075473956586428</v>
+        <v>0.0001042449617490811</v>
       </c>
     </row>
     <row r="333">
@@ -10427,7 +10427,7 @@
         <v>19</v>
       </c>
       <c r="H333" t="n">
-        <v>0.003387412954226653</v>
+        <v>0.1005592520921521</v>
       </c>
     </row>
     <row r="334">
@@ -10457,7 +10457,7 @@
         <v>33</v>
       </c>
       <c r="H334" t="n">
-        <v>0.6942687772571378</v>
+        <v>0.0009487447078504959</v>
       </c>
     </row>
     <row r="335">
@@ -10487,7 +10487,7 @@
         <v>2</v>
       </c>
       <c r="H335" t="n">
-        <v>7.400920130139417e-10</v>
+        <v>6.157599470722567e-10</v>
       </c>
     </row>
     <row r="336">
@@ -10517,7 +10517,7 @@
         <v>14</v>
       </c>
       <c r="H336" t="n">
-        <v>0.9808953740915199</v>
+        <v>0.9939150469706336</v>
       </c>
     </row>
     <row r="337">
@@ -10547,7 +10547,7 @@
         <v>9</v>
       </c>
       <c r="H337" t="n">
-        <v>6.851201880641909e-08</v>
+        <v>1.098210935747191e-08</v>
       </c>
     </row>
     <row r="338">
@@ -10577,7 +10577,7 @@
         <v>12</v>
       </c>
       <c r="H338" t="n">
-        <v>2.771409003320405e-08</v>
+        <v>6.557810215174851e-09</v>
       </c>
     </row>
     <row r="339">
@@ -10607,7 +10607,7 @@
         <v>6</v>
       </c>
       <c r="H339" t="n">
-        <v>0.0002061143569370241</v>
+        <v>4.602409914989918e-07</v>
       </c>
     </row>
     <row r="340">
@@ -10637,7 +10637,7 @@
         <v>15</v>
       </c>
       <c r="H340" t="n">
-        <v>0.4071653183705428</v>
+        <v>0.4728126563513702</v>
       </c>
     </row>
     <row r="341">
@@ -10667,7 +10667,7 @@
         <v>13</v>
       </c>
       <c r="H341" t="n">
-        <v>0.000115930781681537</v>
+        <v>3.773603817667384e-05</v>
       </c>
     </row>
     <row r="342">
@@ -10697,7 +10697,7 @@
         <v>7</v>
       </c>
       <c r="H342" t="n">
-        <v>0.01291486840913099</v>
+        <v>0.9171699675305864</v>
       </c>
     </row>
     <row r="343">
@@ -10727,7 +10727,7 @@
         <v>6</v>
       </c>
       <c r="H343" t="n">
-        <v>0.05698684954650331</v>
+        <v>0.01159136915280361</v>
       </c>
     </row>
     <row r="344">
@@ -10757,7 +10757,7 @@
         <v>6</v>
       </c>
       <c r="H344" t="n">
-        <v>0.04061938278846525</v>
+        <v>0.01182667004290574</v>
       </c>
     </row>
     <row r="345">
@@ -10787,7 +10787,7 @@
         <v>3</v>
       </c>
       <c r="H345" t="n">
-        <v>4.38151550267924e-05</v>
+        <v>0.0001773114407904917</v>
       </c>
     </row>
     <row r="346">
@@ -10817,7 +10817,7 @@
         <v>8</v>
       </c>
       <c r="H346" t="n">
-        <v>0.001661419425794412</v>
+        <v>0.004436805896479977</v>
       </c>
     </row>
     <row r="347">
@@ -10847,7 +10847,7 @@
         <v>8</v>
       </c>
       <c r="H347" t="n">
-        <v>0.01080016822630274</v>
+        <v>0.0002424644878022007</v>
       </c>
     </row>
     <row r="348">
@@ -10877,7 +10877,7 @@
         <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>0.0008195804746868791</v>
+        <v>0.01214781862378956</v>
       </c>
     </row>
     <row r="349">
@@ -10907,7 +10907,7 @@
         <v>5</v>
       </c>
       <c r="H349" t="n">
-        <v>2.747855442648767e-05</v>
+        <v>8.121105689998899e-05</v>
       </c>
     </row>
     <row r="350">
@@ -10937,7 +10937,7 @@
         <v>14</v>
       </c>
       <c r="H350" t="n">
-        <v>0.8256726463334482</v>
+        <v>0.004922598067306844</v>
       </c>
     </row>
     <row r="351">
@@ -10967,7 +10967,7 @@
         <v>6</v>
       </c>
       <c r="H351" t="n">
-        <v>1.519636894785565e-06</v>
+        <v>9.464398749640484e-06</v>
       </c>
     </row>
     <row r="352">
@@ -10997,7 +10997,7 @@
         <v>5</v>
       </c>
       <c r="H352" t="n">
-        <v>0.0003034110592562336</v>
+        <v>1.549666119247747e-08</v>
       </c>
     </row>
     <row r="353">
@@ -11027,7 +11027,7 @@
         <v>8</v>
       </c>
       <c r="H353" t="n">
-        <v>9.892532728953222e-07</v>
+        <v>3.209913112260561e-07</v>
       </c>
     </row>
     <row r="354">
@@ -11057,7 +11057,7 @@
         <v>17</v>
       </c>
       <c r="H354" t="n">
-        <v>1.419678869647982e-07</v>
+        <v>1.145510346541331e-06</v>
       </c>
     </row>
     <row r="355">
@@ -11087,7 +11087,7 @@
         <v>18</v>
       </c>
       <c r="H355" t="n">
-        <v>0.996115316447759</v>
+        <v>0.9999855416988426</v>
       </c>
     </row>
     <row r="356">
@@ -11117,7 +11117,7 @@
         <v>5</v>
       </c>
       <c r="H356" t="n">
-        <v>1.660361542197359e-06</v>
+        <v>9.026286708315221e-06</v>
       </c>
     </row>
     <row r="357">
@@ -11147,7 +11147,7 @@
         <v>8</v>
       </c>
       <c r="H357" t="n">
-        <v>0.0001697122719984272</v>
+        <v>0.008960989600854796</v>
       </c>
     </row>
     <row r="358">
@@ -11177,7 +11177,7 @@
         <v>8</v>
       </c>
       <c r="H358" t="n">
-        <v>0.997186797375433</v>
+        <v>0.0008087499647489074</v>
       </c>
     </row>
     <row r="359">
@@ -11207,7 +11207,7 @@
         <v>15</v>
       </c>
       <c r="H359" t="n">
-        <v>0.9992377345262244</v>
+        <v>0.3223795987760014</v>
       </c>
     </row>
     <row r="360">
@@ -11237,7 +11237,7 @@
         <v>8</v>
       </c>
       <c r="H360" t="n">
-        <v>0.0007298540376351676</v>
+        <v>0.04120012704074224</v>
       </c>
     </row>
     <row r="361">
@@ -11267,7 +11267,7 @@
         <v>15</v>
       </c>
       <c r="H361" t="n">
-        <v>0.1721991138341349</v>
+        <v>0.06016559564934353</v>
       </c>
     </row>
     <row r="362">
@@ -11297,7 +11297,7 @@
         <v>6</v>
       </c>
       <c r="H362" t="n">
-        <v>0.0001793408909892386</v>
+        <v>1.27346017548767e-06</v>
       </c>
     </row>
     <row r="363">
@@ -11327,7 +11327,7 @@
         <v>4</v>
       </c>
       <c r="H363" t="n">
-        <v>0.02444663347435</v>
+        <v>0.01043161789291447</v>
       </c>
     </row>
     <row r="364">
@@ -11357,7 +11357,7 @@
         <v>5</v>
       </c>
       <c r="H364" t="n">
-        <v>0.005280667101162151</v>
+        <v>0.04985450585279894</v>
       </c>
     </row>
     <row r="365">
@@ -11387,7 +11387,7 @@
         <v>5</v>
       </c>
       <c r="H365" t="n">
-        <v>3.922688942367283e-06</v>
+        <v>7.511148211495431e-07</v>
       </c>
     </row>
     <row r="366">
@@ -11417,7 +11417,7 @@
         <v>5</v>
       </c>
       <c r="H366" t="n">
-        <v>0.002574628069703359</v>
+        <v>0.9813019828392544</v>
       </c>
     </row>
     <row r="367">
@@ -11447,7 +11447,7 @@
         <v>11</v>
       </c>
       <c r="H367" t="n">
-        <v>2.138936893426483e-05</v>
+        <v>0.02264137808095748</v>
       </c>
     </row>
     <row r="368">
@@ -11477,7 +11477,7 @@
         <v>14</v>
       </c>
       <c r="H368" t="n">
-        <v>0.008148025320987193</v>
+        <v>0.9676476016556524</v>
       </c>
     </row>
     <row r="369">
@@ -11507,7 +11507,7 @@
         <v>3</v>
       </c>
       <c r="H369" t="n">
-        <v>0.0007275622477719391</v>
+        <v>0.0003950462952066334</v>
       </c>
     </row>
     <row r="370">
@@ -11537,7 +11537,7 @@
         <v>3</v>
       </c>
       <c r="H370" t="n">
-        <v>0.05482145191663081</v>
+        <v>0.01503471338485061</v>
       </c>
     </row>
     <row r="371">
@@ -11567,7 +11567,7 @@
         <v>14</v>
       </c>
       <c r="H371" t="n">
-        <v>0.998553331950316</v>
+        <v>0.9918006348254474</v>
       </c>
     </row>
     <row r="372">
@@ -11597,7 +11597,7 @@
         <v>5</v>
       </c>
       <c r="H372" t="n">
-        <v>0.001643647303043017</v>
+        <v>0.0005592944266508713</v>
       </c>
     </row>
     <row r="373">
@@ -11627,7 +11627,7 @@
         <v>4</v>
       </c>
       <c r="H373" t="n">
-        <v>0.02385990233892466</v>
+        <v>0.007007709148195025</v>
       </c>
     </row>
     <row r="374">
@@ -11657,7 +11657,7 @@
         <v>5</v>
       </c>
       <c r="H374" t="n">
-        <v>2.380510373104397e-07</v>
+        <v>1.845698904996309e-08</v>
       </c>
     </row>
     <row r="375">
@@ -11687,7 +11687,7 @@
         <v>5</v>
       </c>
       <c r="H375" t="n">
-        <v>0.006743937131927482</v>
+        <v>0.00131938059943993</v>
       </c>
     </row>
     <row r="376">
@@ -11717,7 +11717,7 @@
         <v>8</v>
       </c>
       <c r="H376" t="n">
-        <v>2.178480584277814e-06</v>
+        <v>0.0005732232735083412</v>
       </c>
     </row>
     <row r="377">
@@ -11747,7 +11747,7 @@
         <v>7</v>
       </c>
       <c r="H377" t="n">
-        <v>0.1227788165055595</v>
+        <v>0.9076588659728982</v>
       </c>
     </row>
     <row r="378">
@@ -11777,7 +11777,7 @@
         <v>3</v>
       </c>
       <c r="H378" t="n">
-        <v>0.1867382423707018</v>
+        <v>0.4029104518617376</v>
       </c>
     </row>
     <row r="379">
@@ -11807,7 +11807,7 @@
         <v>9</v>
       </c>
       <c r="H379" t="n">
-        <v>0.005809164520010225</v>
+        <v>0.0001221540340353897</v>
       </c>
     </row>
     <row r="380">
@@ -11837,7 +11837,7 @@
         <v>0.7368421052631579</v>
       </c>
       <c r="H380" t="n">
-        <v>0.2771514495025066</v>
+        <v>0.3334301553622425</v>
       </c>
     </row>
     <row r="381">
@@ -11867,7 +11867,7 @@
         <v>1.81578947368421</v>
       </c>
       <c r="H381" t="n">
-        <v>0.1738464756309439</v>
+        <v>0.0102828000099955</v>
       </c>
     </row>
     <row r="382">
@@ -11897,7 +11897,7 @@
         <v>7.736842105263157</v>
       </c>
       <c r="H382" t="n">
-        <v>0.9989906996002674</v>
+        <v>0.9999679013688293</v>
       </c>
     </row>
     <row r="383">
@@ -11927,7 +11927,7 @@
         <v>2.289473684210526</v>
       </c>
       <c r="H383" t="n">
-        <v>0.7362153215996726</v>
+        <v>0.003953632063527562</v>
       </c>
     </row>
     <row r="384">
@@ -11957,7 +11957,7 @@
         <v>2</v>
       </c>
       <c r="H384" t="n">
-        <v>0.8252403254626378</v>
+        <v>0.6640671482865126</v>
       </c>
     </row>
     <row r="385">
@@ -11987,7 +11987,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="H385" t="n">
-        <v>0.4507702517001734</v>
+        <v>0.8259489619296391</v>
       </c>
     </row>
     <row r="386">
@@ -12017,7 +12017,7 @@
         <v>1.473684210526316</v>
       </c>
       <c r="H386" t="n">
-        <v>0.9765195016059646</v>
+        <v>0.9600493580246897</v>
       </c>
     </row>
     <row r="387">
@@ -12047,7 +12047,7 @@
         <v>2.105263157894737</v>
       </c>
       <c r="H387" t="n">
-        <v>0.5308082668229648</v>
+        <v>0.6600128368415039</v>
       </c>
     </row>
     <row r="388">
@@ -12077,7 +12077,7 @@
         <v>1.263157894736842</v>
       </c>
       <c r="H388" t="n">
-        <v>0.9041538419665287</v>
+        <v>0.1161236041826087</v>
       </c>
     </row>
     <row r="389">
@@ -12107,7 +12107,7 @@
         <v>0.6842105263157895</v>
       </c>
       <c r="H389" t="n">
-        <v>0.00532497812224171</v>
+        <v>0.1622869072753495</v>
       </c>
     </row>
     <row r="390">
@@ -12137,7 +12137,7 @@
         <v>3.473684210526316</v>
       </c>
       <c r="H390" t="n">
-        <v>2.47251788105103e-05</v>
+        <v>0.0001844863047951023</v>
       </c>
     </row>
     <row r="391">
@@ -12167,7 +12167,7 @@
         <v>2.763157894736842</v>
       </c>
       <c r="H391" t="n">
-        <v>4.761952179488721e-06</v>
+        <v>0.0001856358190122779</v>
       </c>
     </row>
     <row r="392">
@@ -12197,7 +12197,7 @@
         <v>1.552631578947368</v>
       </c>
       <c r="H392" t="n">
-        <v>0.60105142675652</v>
+        <v>0.5674790657830596</v>
       </c>
     </row>
     <row r="393">
@@ -12227,7 +12227,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H393" t="n">
-        <v>0.03752428499596427</v>
+        <v>0.08803290427386642</v>
       </c>
     </row>
     <row r="394">
@@ -12257,7 +12257,7 @@
         <v>1.947368421052632</v>
       </c>
       <c r="H394" t="n">
-        <v>0.09140954984934657</v>
+        <v>0.1061922027031764</v>
       </c>
     </row>
     <row r="395">
@@ -12287,7 +12287,7 @@
         <v>3.5</v>
       </c>
       <c r="H395" t="n">
-        <v>0.2525646300857361</v>
+        <v>0.01879267269133574</v>
       </c>
     </row>
     <row r="396">
@@ -12317,7 +12317,7 @@
         <v>1.263157894736842</v>
       </c>
       <c r="H396" t="n">
-        <v>0.9341066373091138</v>
+        <v>0.6791983374326319</v>
       </c>
     </row>
     <row r="397">
@@ -12347,7 +12347,7 @@
         <v>1.736842105263158</v>
       </c>
       <c r="H397" t="n">
-        <v>8.179170420395024e-07</v>
+        <v>0.00215283617806883</v>
       </c>
     </row>
     <row r="398">
@@ -12377,7 +12377,7 @@
         <v>1.552631578947368</v>
       </c>
       <c r="H398" t="n">
-        <v>3.684508263546313e-05</v>
+        <v>0.009178870436182575</v>
       </c>
     </row>
     <row r="399">
@@ -12407,7 +12407,7 @@
         <v>2.052631578947369</v>
       </c>
       <c r="H399" t="n">
-        <v>0.9782032054625895</v>
+        <v>0.826050487178664</v>
       </c>
     </row>
     <row r="400">
@@ -12437,7 +12437,7 @@
         <v>2.394736842105264</v>
       </c>
       <c r="H400" t="n">
-        <v>0.921698900003891</v>
+        <v>0.9514704481584978</v>
       </c>
     </row>
     <row r="401">
@@ -12467,7 +12467,7 @@
         <v>1.078947368421053</v>
       </c>
       <c r="H401" t="n">
-        <v>0.5004638147766021</v>
+        <v>0.9912600937156179</v>
       </c>
     </row>
     <row r="402">
@@ -12497,7 +12497,7 @@
         <v>2.289473684210526</v>
       </c>
       <c r="H402" t="n">
-        <v>0.9665530483115644</v>
+        <v>0.2574370982887818</v>
       </c>
     </row>
     <row r="403">
@@ -12527,7 +12527,7 @@
         <v>1.973684210526316</v>
       </c>
       <c r="H403" t="n">
-        <v>0.9396640196499599</v>
+        <v>0.1634363193461019</v>
       </c>
     </row>
     <row r="404">
@@ -12557,7 +12557,7 @@
         <v>8.973684210526315</v>
       </c>
       <c r="H404" t="n">
-        <v>0.9999999999941669</v>
+        <v>0.9999999983147527</v>
       </c>
     </row>
     <row r="405">
@@ -12587,7 +12587,7 @@
         <v>2.210526315789474</v>
       </c>
       <c r="H405" t="n">
-        <v>0.007484614966042151</v>
+        <v>0.0030121907472842</v>
       </c>
     </row>
     <row r="406">
@@ -12617,7 +12617,7 @@
         <v>2.605263157894737</v>
       </c>
       <c r="H406" t="n">
-        <v>1.040309045138139e-05</v>
+        <v>0.0001992368972458549</v>
       </c>
     </row>
     <row r="407">
@@ -12647,7 +12647,7 @@
         <v>1.868421052631579</v>
       </c>
       <c r="H407" t="n">
-        <v>9.586609714411217e-06</v>
+        <v>7.819922761645011e-06</v>
       </c>
     </row>
     <row r="408">
@@ -12677,7 +12677,7 @@
         <v>3.289473684210526</v>
       </c>
       <c r="H408" t="n">
-        <v>0.0001938915731379173</v>
+        <v>0.0001861450737247951</v>
       </c>
     </row>
     <row r="409">
@@ -12707,7 +12707,7 @@
         <v>6.447368421052632</v>
       </c>
       <c r="H409" t="n">
-        <v>0.7631313231763619</v>
+        <v>0.7244287999009752</v>
       </c>
     </row>
     <row r="410">
@@ -12737,7 +12737,7 @@
         <v>4.157894736842105</v>
       </c>
       <c r="H410" t="n">
-        <v>0.03852852275195368</v>
+        <v>0.04972534688153683</v>
       </c>
     </row>
     <row r="411">
@@ -12767,7 +12767,7 @@
         <v>10.89473684210526</v>
       </c>
       <c r="H411" t="n">
-        <v>0.8418672376954037</v>
+        <v>0.8905358955853329</v>
       </c>
     </row>
     <row r="412">
@@ -12797,7 +12797,7 @@
         <v>8.184210526315789</v>
       </c>
       <c r="H412" t="n">
-        <v>0.9966395202209695</v>
+        <v>0.9971394204263624</v>
       </c>
     </row>
     <row r="413">
@@ -12827,7 +12827,7 @@
         <v>7.578947368421052</v>
       </c>
       <c r="H413" t="n">
-        <v>0.4409446549811396</v>
+        <v>0.3630079559721045</v>
       </c>
     </row>
     <row r="414">
@@ -12857,7 +12857,7 @@
         <v>60.42105263157895</v>
       </c>
       <c r="H414" t="n">
-        <v>0.01126676199645959</v>
+        <v>0.002823239687159435</v>
       </c>
     </row>
     <row r="415">
@@ -12887,7 +12887,7 @@
         <v>17.84210526315789</v>
       </c>
       <c r="H415" t="n">
-        <v>0.7828298636861566</v>
+        <v>0.8216223937558588</v>
       </c>
     </row>
     <row r="416">
@@ -12917,7 +12917,7 @@
         <v>1.894736842105263</v>
       </c>
       <c r="H416" t="n">
-        <v>0.974386179498718</v>
+        <v>0.9770155445041512</v>
       </c>
     </row>
     <row r="417">
@@ -12947,7 +12947,7 @@
         <v>2.763157894736842</v>
       </c>
       <c r="H417" t="n">
-        <v>0.01530175490955799</v>
+        <v>0.006287599968778829</v>
       </c>
     </row>
     <row r="418">
@@ -12977,7 +12977,7 @@
         <v>3.473684210526316</v>
       </c>
       <c r="H418" t="n">
-        <v>0.2861420761011658</v>
+        <v>0.288658961530163</v>
       </c>
     </row>
     <row r="419">
@@ -13007,7 +13007,7 @@
         <v>1.026315789473684</v>
       </c>
       <c r="H419" t="n">
-        <v>0.7202305070708753</v>
+        <v>0.7830466864803612</v>
       </c>
     </row>
     <row r="420">
@@ -13037,7 +13037,7 @@
         <v>10.10526315789474</v>
       </c>
       <c r="H420" t="n">
-        <v>0.9848256518421572</v>
+        <v>0.9889308115948025</v>
       </c>
     </row>
     <row r="421">
@@ -13067,7 +13067,7 @@
         <v>29.84210526315789</v>
       </c>
       <c r="H421" t="n">
-        <v>0.9998474779846314</v>
+        <v>0.9998219344411359</v>
       </c>
     </row>
     <row r="422">
@@ -13097,7 +13097,7 @@
         <v>2.394736842105264</v>
       </c>
       <c r="H422" t="n">
-        <v>0.001936813104789903</v>
+        <v>0.001186639211270168</v>
       </c>
     </row>
     <row r="423">
@@ -13127,7 +13127,7 @@
         <v>2.078947368421053</v>
       </c>
       <c r="H423" t="n">
-        <v>0.2371616002828862</v>
+        <v>0.3488257274957022</v>
       </c>
     </row>
     <row r="424">
@@ -13157,7 +13157,7 @@
         <v>2.368421052631579</v>
       </c>
       <c r="H424" t="n">
-        <v>0.0001021857715190435</v>
+        <v>0.0001344015127992486</v>
       </c>
     </row>
     <row r="425">
@@ -13187,7 +13187,7 @@
         <v>19.07894736842105</v>
       </c>
       <c r="H425" t="n">
-        <v>0.9950801491260325</v>
+        <v>0.9957463912467037</v>
       </c>
     </row>
     <row r="426">
@@ -13217,7 +13217,7 @@
         <v>2.421052631578948</v>
       </c>
       <c r="H426" t="n">
-        <v>0.04857015350790176</v>
+        <v>0.07363462766967709</v>
       </c>
     </row>
     <row r="427">
@@ -13247,7 +13247,7 @@
         <v>2.289473684210526</v>
       </c>
       <c r="H427" t="n">
-        <v>0.0605248795508114</v>
+        <v>0.05496587304971968</v>
       </c>
     </row>
     <row r="428">
@@ -13277,7 +13277,7 @@
         <v>17.15789473684211</v>
       </c>
       <c r="H428" t="n">
-        <v>0.9998704934976177</v>
+        <v>0.9999250650744512</v>
       </c>
     </row>
     <row r="429">
@@ -13307,7 +13307,7 @@
         <v>7.052631578947368</v>
       </c>
       <c r="H429" t="n">
-        <v>0.9877123588154855</v>
+        <v>0.975072678127793</v>
       </c>
     </row>
     <row r="430">
@@ -13337,7 +13337,7 @@
         <v>7.947368421052632</v>
       </c>
       <c r="H430" t="n">
-        <v>0.9668626135062219</v>
+        <v>0.9659499307103677</v>
       </c>
     </row>
     <row r="431">
@@ -13367,7 +13367,7 @@
         <v>1.312849162011173</v>
       </c>
       <c r="H431" t="n">
-        <v>0.03828404194078289</v>
+        <v>0.04173141983176665</v>
       </c>
     </row>
     <row r="432">
@@ -13397,7 +13397,7 @@
         <v>11.11731843575419</v>
       </c>
       <c r="H432" t="n">
-        <v>0.9886515696235019</v>
+        <v>0.9890158291315072</v>
       </c>
     </row>
     <row r="433">
@@ -13427,7 +13427,7 @@
         <v>2.122905027932961</v>
       </c>
       <c r="H433" t="n">
-        <v>0.0004572917453189927</v>
+        <v>0.0003646261398681655</v>
       </c>
     </row>
     <row r="434">
@@ -13457,7 +13457,7 @@
         <v>5.251396648044693</v>
       </c>
       <c r="H434" t="n">
-        <v>0.5509625526069378</v>
+        <v>0.5129136196819223</v>
       </c>
     </row>
     <row r="435">
@@ -13487,7 +13487,7 @@
         <v>14.6927374301676</v>
       </c>
       <c r="H435" t="n">
-        <v>0.9998420994024921</v>
+        <v>0.9998238037700277</v>
       </c>
     </row>
     <row r="436">
@@ -13517,7 +13517,7 @@
         <v>13.10055865921788</v>
       </c>
       <c r="H436" t="n">
-        <v>0.9998463105875062</v>
+        <v>0.9998916295040803</v>
       </c>
     </row>
     <row r="437">
@@ -13547,7 +13547,7 @@
         <v>10.97765363128492</v>
       </c>
       <c r="H437" t="n">
-        <v>0.9501268973723692</v>
+        <v>0.9599117258448218</v>
       </c>
     </row>
     <row r="438">
@@ -13577,7 +13577,7 @@
         <v>11.89944134078212</v>
       </c>
       <c r="H438" t="n">
-        <v>0.9999641791518208</v>
+        <v>0.9999690166736153</v>
       </c>
     </row>
     <row r="439">
@@ -13607,7 +13607,7 @@
         <v>9.022346368715084</v>
       </c>
       <c r="H439" t="n">
-        <v>0.2767678741832359</v>
+        <v>0.3463107291632971</v>
       </c>
     </row>
     <row r="440">
@@ -13637,7 +13637,7 @@
         <v>17.59776536312849</v>
       </c>
       <c r="H440" t="n">
-        <v>0.9999684756610008</v>
+        <v>0.9999700961987378</v>
       </c>
     </row>
     <row r="441">
@@ -13667,7 +13667,7 @@
         <v>6.089385474860336</v>
       </c>
       <c r="H441" t="n">
-        <v>0.9984306056232088</v>
+        <v>0.9982843163621294</v>
       </c>
     </row>
     <row r="442">
@@ -13697,7 +13697,7 @@
         <v>10.11173184357542</v>
       </c>
       <c r="H442" t="n">
-        <v>0.9448686082903484</v>
+        <v>0.9332184399185267</v>
       </c>
     </row>
     <row r="443">
@@ -13727,7 +13727,7 @@
         <v>9.608938547486034</v>
       </c>
       <c r="H443" t="n">
-        <v>0.9284277648108937</v>
+        <v>0.8872285317394991</v>
       </c>
     </row>
     <row r="444">
@@ -13757,7 +13757,7 @@
         <v>4.273743016759777</v>
       </c>
       <c r="H444" t="n">
-        <v>0.01888968776427694</v>
+        <v>0.02172957133938409</v>
       </c>
     </row>
     <row r="445">
@@ -13787,7 +13787,7 @@
         <v>4.385474860335196</v>
       </c>
       <c r="H445" t="n">
-        <v>0.1372521198939096</v>
+        <v>0.1347322852371048</v>
       </c>
     </row>
     <row r="446">
@@ -13817,7 +13817,7 @@
         <v>7</v>
       </c>
       <c r="H446" t="n">
-        <v>0.007053972836360662</v>
+        <v>0.001834745900921692</v>
       </c>
     </row>
     <row r="447">
@@ -13847,7 +13847,7 @@
         <v>5</v>
       </c>
       <c r="H447" t="n">
-        <v>0.4799924813154597</v>
+        <v>0.1435956676654281</v>
       </c>
     </row>
     <row r="448">
@@ -13877,7 +13877,7 @@
         <v>6</v>
       </c>
       <c r="H448" t="n">
-        <v>0.001844383975592481</v>
+        <v>0.001070565919516409</v>
       </c>
     </row>
     <row r="449">
@@ -13907,7 +13907,7 @@
         <v>5</v>
       </c>
       <c r="H449" t="n">
-        <v>3.957705399561194e-05</v>
+        <v>8.723785494684655e-06</v>
       </c>
     </row>
     <row r="450">
@@ -13937,7 +13937,7 @@
         <v>12</v>
       </c>
       <c r="H450" t="n">
-        <v>1.628796126782989e-08</v>
+        <v>4.787387008187247e-07</v>
       </c>
     </row>
     <row r="451">
@@ -13967,7 +13967,7 @@
         <v>22</v>
       </c>
       <c r="H451" t="n">
-        <v>4.041191682674576e-06</v>
+        <v>1.933233782605777e-07</v>
       </c>
     </row>
     <row r="452">
@@ -13997,7 +13997,7 @@
         <v>1</v>
       </c>
       <c r="H452" t="n">
-        <v>4.589538617225396e-06</v>
+        <v>1.131979557549253e-05</v>
       </c>
     </row>
     <row r="453">
@@ -14027,7 +14027,7 @@
         <v>2</v>
       </c>
       <c r="H453" t="n">
-        <v>0.2057744688177174</v>
+        <v>0.2380047708204872</v>
       </c>
     </row>
     <row r="454">
@@ -14057,7 +14057,7 @@
         <v>23</v>
       </c>
       <c r="H454" t="n">
-        <v>0.003516138305587404</v>
+        <v>0.08160081798295458</v>
       </c>
     </row>
     <row r="455">
@@ -14087,7 +14087,7 @@
         <v>8</v>
       </c>
       <c r="H455" t="n">
-        <v>2.292487694284435e-06</v>
+        <v>1.046667393389593e-07</v>
       </c>
     </row>
     <row r="456">
@@ -14117,7 +14117,7 @@
         <v>1</v>
       </c>
       <c r="H456" t="n">
-        <v>0.005597614257303048</v>
+        <v>0.1120194394138311</v>
       </c>
     </row>
     <row r="457">
@@ -14147,7 +14147,7 @@
         <v>6</v>
       </c>
       <c r="H457" t="n">
-        <v>0.005881682074262436</v>
+        <v>0.0014251412585592</v>
       </c>
     </row>
     <row r="458">
@@ -14177,7 +14177,7 @@
         <v>8</v>
       </c>
       <c r="H458" t="n">
-        <v>6.436026495781373e-05</v>
+        <v>0.0006466535950730252</v>
       </c>
     </row>
     <row r="459">
@@ -14207,7 +14207,7 @@
         <v>17</v>
       </c>
       <c r="H459" t="n">
-        <v>0.0001932347075568167</v>
+        <v>0.03455481743756132</v>
       </c>
     </row>
     <row r="460">
@@ -14237,7 +14237,7 @@
         <v>8</v>
       </c>
       <c r="H460" t="n">
-        <v>0.02930657650185263</v>
+        <v>0.001394092993643651</v>
       </c>
     </row>
     <row r="461">
@@ -14267,7 +14267,7 @@
         <v>8</v>
       </c>
       <c r="H461" t="n">
-        <v>0.1506231365651641</v>
+        <v>0.2703674232688957</v>
       </c>
     </row>
     <row r="462">
@@ -14297,7 +14297,7 @@
         <v>0</v>
       </c>
       <c r="H462" t="n">
-        <v>0.0001636789163147518</v>
+        <v>0.0002958026292578799</v>
       </c>
     </row>
     <row r="463">
@@ -14327,7 +14327,7 @@
         <v>5</v>
       </c>
       <c r="H463" t="n">
-        <v>0.0001639665339628843</v>
+        <v>0.0004591346776264952</v>
       </c>
     </row>
     <row r="464">
@@ -14357,7 +14357,7 @@
         <v>59</v>
       </c>
       <c r="H464" t="n">
-        <v>0.9855917793106216</v>
+        <v>0.04409712935038872</v>
       </c>
     </row>
     <row r="465">
@@ -14387,7 +14387,7 @@
         <v>12</v>
       </c>
       <c r="H465" t="n">
-        <v>1.321297921398869e-05</v>
+        <v>1.04360155259597e-06</v>
       </c>
     </row>
     <row r="466">
@@ -14417,7 +14417,7 @@
         <v>8</v>
       </c>
       <c r="H466" t="n">
-        <v>4.100143048714695e-05</v>
+        <v>9.955316500569842e-07</v>
       </c>
     </row>
     <row r="467">
@@ -14447,7 +14447,7 @@
         <v>14</v>
       </c>
       <c r="H467" t="n">
-        <v>0.9999232541182723</v>
+        <v>0.99999945307393</v>
       </c>
     </row>
     <row r="468">
@@ -14477,7 +14477,7 @@
         <v>9</v>
       </c>
       <c r="H468" t="n">
-        <v>0.9457469770955999</v>
+        <v>0.9649710106116706</v>
       </c>
     </row>
     <row r="469">
@@ -14507,7 +14507,7 @@
         <v>8</v>
       </c>
       <c r="H469" t="n">
-        <v>2.712028635892084e-06</v>
+        <v>8.562600398858574e-05</v>
       </c>
     </row>
     <row r="470">
@@ -14537,7 +14537,7 @@
         <v>5</v>
       </c>
       <c r="H470" t="n">
-        <v>0.000950338434979929</v>
+        <v>0.5372550501843517</v>
       </c>
     </row>
     <row r="471">
@@ -14567,7 +14567,7 @@
         <v>8</v>
       </c>
       <c r="H471" t="n">
-        <v>6.664158604568822e-06</v>
+        <v>1.24614136135923e-08</v>
       </c>
     </row>
     <row r="472">
@@ -14597,7 +14597,7 @@
         <v>7</v>
       </c>
       <c r="H472" t="n">
-        <v>2.24567959620857e-07</v>
+        <v>1.951145311542321e-05</v>
       </c>
     </row>
     <row r="473">
@@ -14627,7 +14627,7 @@
         <v>5</v>
       </c>
       <c r="H473" t="n">
-        <v>5.129232749278587e-05</v>
+        <v>0.0005887755178112292</v>
       </c>
     </row>
     <row r="474">
@@ -14657,7 +14657,7 @@
         <v>4</v>
       </c>
       <c r="H474" t="n">
-        <v>1.818359555455266e-07</v>
+        <v>6.697298005162148e-05</v>
       </c>
     </row>
     <row r="475">
@@ -14687,7 +14687,7 @@
         <v>8</v>
       </c>
       <c r="H475" t="n">
-        <v>0.0002752584897399683</v>
+        <v>0.0225730350255067</v>
       </c>
     </row>
     <row r="476">
@@ -14717,7 +14717,7 @@
         <v>8</v>
       </c>
       <c r="H476" t="n">
-        <v>2.676520250847914e-07</v>
+        <v>5.044863447295373e-07</v>
       </c>
     </row>
     <row r="477">
@@ -14747,7 +14747,7 @@
         <v>13</v>
       </c>
       <c r="H477" t="n">
-        <v>0.9936666783144954</v>
+        <v>0.8861757426159108</v>
       </c>
     </row>
     <row r="478">
@@ -14777,7 +14777,7 @@
         <v>7</v>
       </c>
       <c r="H478" t="n">
-        <v>0.9872372076402021</v>
+        <v>0.9907890853773464</v>
       </c>
     </row>
     <row r="479">
@@ -14807,7 +14807,7 @@
         <v>12</v>
       </c>
       <c r="H479" t="n">
-        <v>0.2172438138370825</v>
+        <v>0.2066385732568227</v>
       </c>
     </row>
     <row r="480">
@@ -14837,7 +14837,7 @@
         <v>10</v>
       </c>
       <c r="H480" t="n">
-        <v>0.0002146108585106191</v>
+        <v>0.07449342877218286</v>
       </c>
     </row>
     <row r="481">
@@ -14867,7 +14867,7 @@
         <v>8</v>
       </c>
       <c r="H481" t="n">
-        <v>0.7947217390429056</v>
+        <v>0.06671477805330812</v>
       </c>
     </row>
     <row r="482">
@@ -14897,7 +14897,7 @@
         <v>8</v>
       </c>
       <c r="H482" t="n">
-        <v>0.1823586544723484</v>
+        <v>0.006402517587283638</v>
       </c>
     </row>
     <row r="483">
@@ -14927,7 +14927,7 @@
         <v>14</v>
       </c>
       <c r="H483" t="n">
-        <v>0.8707838381276435</v>
+        <v>0.9342759939068171</v>
       </c>
     </row>
     <row r="484">
@@ -14957,7 +14957,7 @@
         <v>7</v>
       </c>
       <c r="H484" t="n">
-        <v>3.923362697702357e-08</v>
+        <v>1.730258838451186e-09</v>
       </c>
     </row>
     <row r="485">
@@ -14987,7 +14987,7 @@
         <v>19</v>
       </c>
       <c r="H485" t="n">
-        <v>0.9997918116433206</v>
+        <v>0.9999990786269082</v>
       </c>
     </row>
     <row r="486">
@@ -15017,7 +15017,7 @@
         <v>8</v>
       </c>
       <c r="H486" t="n">
-        <v>3.646570941393241e-07</v>
+        <v>0.0009784644359512717</v>
       </c>
     </row>
     <row r="487">
@@ -15047,7 +15047,7 @@
         <v>10</v>
       </c>
       <c r="H487" t="n">
-        <v>0.0120221794794737</v>
+        <v>0.005647033511543931</v>
       </c>
     </row>
     <row r="488">
@@ -15077,7 +15077,7 @@
         <v>3</v>
       </c>
       <c r="H488" t="n">
-        <v>0.000583648719133807</v>
+        <v>0.0001736223200652672</v>
       </c>
     </row>
     <row r="489">
@@ -15107,7 +15107,7 @@
         <v>10</v>
       </c>
       <c r="H489" t="n">
-        <v>0.01422818074505087</v>
+        <v>0.06129446835213936</v>
       </c>
     </row>
     <row r="490">
@@ -15137,7 +15137,7 @@
         <v>8</v>
       </c>
       <c r="H490" t="n">
-        <v>0.006041306948041589</v>
+        <v>0.04002427329270868</v>
       </c>
     </row>
     <row r="491">
@@ -15167,7 +15167,7 @@
         <v>8</v>
       </c>
       <c r="H491" t="n">
-        <v>5.808994640038556e-07</v>
+        <v>5.703465442962248e-06</v>
       </c>
     </row>
     <row r="492">
@@ -15197,7 +15197,7 @@
         <v>26</v>
       </c>
       <c r="H492" t="n">
-        <v>5.895857072823864e-05</v>
+        <v>6.402581915504827e-06</v>
       </c>
     </row>
     <row r="493">
@@ -15227,7 +15227,7 @@
         <v>62</v>
       </c>
       <c r="H493" t="n">
-        <v>0.9874759044021607</v>
+        <v>0.9999798588270523</v>
       </c>
     </row>
     <row r="494">
@@ -15257,7 +15257,7 @@
         <v>8</v>
       </c>
       <c r="H494" t="n">
-        <v>0.001375148899952856</v>
+        <v>1.237069619374213e-07</v>
       </c>
     </row>
     <row r="495">
@@ -15287,7 +15287,7 @@
         <v>8</v>
       </c>
       <c r="H495" t="n">
-        <v>0.4527923527544567</v>
+        <v>2.128052007281102e-09</v>
       </c>
     </row>
     <row r="496">
@@ -15317,7 +15317,7 @@
         <v>8</v>
       </c>
       <c r="H496" t="n">
-        <v>3.025022840168805e-06</v>
+        <v>0.001014869009898259</v>
       </c>
     </row>
     <row r="497">
@@ -15347,7 +15347,7 @@
         <v>19</v>
       </c>
       <c r="H497" t="n">
-        <v>0.00529631155523056</v>
+        <v>0.003328986928085163</v>
       </c>
     </row>
     <row r="498">
@@ -15377,7 +15377,7 @@
         <v>2</v>
       </c>
       <c r="H498" t="n">
-        <v>6.952636109018883e-06</v>
+        <v>2.713777413335399e-08</v>
       </c>
     </row>
     <row r="499">
@@ -15407,7 +15407,7 @@
         <v>8</v>
       </c>
       <c r="H499" t="n">
-        <v>0.97396667996728</v>
+        <v>0.9977386958891316</v>
       </c>
     </row>
     <row r="500">
@@ -15437,7 +15437,7 @@
         <v>6</v>
       </c>
       <c r="H500" t="n">
-        <v>0.9926669953067546</v>
+        <v>0.9906554237041447</v>
       </c>
     </row>
     <row r="501">
@@ -15467,7 +15467,7 @@
         <v>7</v>
       </c>
       <c r="H501" t="n">
-        <v>0.001867689936485748</v>
+        <v>0.001912412202229897</v>
       </c>
     </row>
     <row r="502">
@@ -15497,7 +15497,7 @@
         <v>2</v>
       </c>
       <c r="H502" t="n">
-        <v>0.01191117936675047</v>
+        <v>0.0002615680099199571</v>
       </c>
     </row>
     <row r="503">
@@ -15527,7 +15527,7 @@
         <v>8</v>
       </c>
       <c r="H503" t="n">
-        <v>0.005453074706492894</v>
+        <v>0.7685043278001242</v>
       </c>
     </row>
     <row r="504">
@@ -15557,7 +15557,7 @@
         <v>8</v>
       </c>
       <c r="H504" t="n">
-        <v>0.02477415817381165</v>
+        <v>0.4459023981219859</v>
       </c>
     </row>
     <row r="505">
@@ -15587,7 +15587,7 @@
         <v>1.657894736842105</v>
       </c>
       <c r="H505" t="n">
-        <v>0.6215229806530109</v>
+        <v>0.1644248897421376</v>
       </c>
     </row>
     <row r="506">
@@ -15617,7 +15617,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="H506" t="n">
-        <v>0.08471856206832316</v>
+        <v>0.3996293163475951</v>
       </c>
     </row>
     <row r="507">
@@ -15647,7 +15647,7 @@
         <v>0.8947368421052632</v>
       </c>
       <c r="H507" t="n">
-        <v>0.9999646193724738</v>
+        <v>0.9999965506453912</v>
       </c>
     </row>
     <row r="508">
@@ -15677,7 +15677,7 @@
         <v>2</v>
       </c>
       <c r="H508" t="n">
-        <v>0.6556636994362822</v>
+        <v>0.02269781230675928</v>
       </c>
     </row>
     <row r="509">
@@ -15707,7 +15707,7 @@
         <v>1.763157894736842</v>
       </c>
       <c r="H509" t="n">
-        <v>0.9219420358238943</v>
+        <v>0.5085291712064619</v>
       </c>
     </row>
     <row r="510">
@@ -15737,7 +15737,7 @@
         <v>1.81578947368421</v>
       </c>
       <c r="H510" t="n">
-        <v>0.848037655642185</v>
+        <v>0.3527760217435421</v>
       </c>
     </row>
     <row r="511">
@@ -15767,7 +15767,7 @@
         <v>1.236842105263158</v>
       </c>
       <c r="H511" t="n">
-        <v>0.9988984701626071</v>
+        <v>0.8016328936634952</v>
       </c>
     </row>
     <row r="512">
@@ -15797,7 +15797,7 @@
         <v>1.210526315789474</v>
       </c>
       <c r="H512" t="n">
-        <v>0.157716408520305</v>
+        <v>0.04982923831890451</v>
       </c>
     </row>
     <row r="513">
@@ -15827,7 +15827,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H513" t="n">
-        <v>0.01832083195713405</v>
+        <v>0.06529138908972856</v>
       </c>
     </row>
     <row r="514">
@@ -15857,7 +15857,7 @@
         <v>2.710526315789474</v>
       </c>
       <c r="H514" t="n">
-        <v>0.9176716929976626</v>
+        <v>0.9920726553127117</v>
       </c>
     </row>
     <row r="515">
@@ -15887,7 +15887,7 @@
         <v>0.7631578947368421</v>
       </c>
       <c r="H515" t="n">
-        <v>0.7221775289012071</v>
+        <v>0.146468042143788</v>
       </c>
     </row>
     <row r="516">
@@ -15917,7 +15917,7 @@
         <v>3.447368421052631</v>
       </c>
       <c r="H516" t="n">
-        <v>0.8669024580519517</v>
+        <v>0.9502949880965416</v>
       </c>
     </row>
     <row r="517">
@@ -15947,7 +15947,7 @@
         <v>0.5</v>
       </c>
       <c r="H517" t="n">
-        <v>0.3831201431594424</v>
+        <v>0.4735080522839673</v>
       </c>
     </row>
     <row r="518">
@@ -15977,7 +15977,7 @@
         <v>1.842105263157895</v>
       </c>
       <c r="H518" t="n">
-        <v>0.01871224776134043</v>
+        <v>0.001384902021997613</v>
       </c>
     </row>
     <row r="519">
@@ -16007,7 +16007,7 @@
         <v>1.473684210526316</v>
       </c>
       <c r="H519" t="n">
-        <v>0.9535346502228522</v>
+        <v>0.4004720982021307</v>
       </c>
     </row>
     <row r="520">
@@ -16037,7 +16037,7 @@
         <v>2.473684210526316</v>
       </c>
       <c r="H520" t="n">
-        <v>0.003932272161093377</v>
+        <v>0.01185544602445866</v>
       </c>
     </row>
     <row r="521">
@@ -16067,7 +16067,7 @@
         <v>2.157894736842105</v>
       </c>
       <c r="H521" t="n">
-        <v>0.9999792235204802</v>
+        <v>0.9996707038449892</v>
       </c>
     </row>
     <row r="522">
@@ -16097,7 +16097,7 @@
         <v>1</v>
       </c>
       <c r="H522" t="n">
-        <v>0.1344247665827671</v>
+        <v>0.2428811403290858</v>
       </c>
     </row>
     <row r="523">
@@ -16127,7 +16127,7 @@
         <v>1.289473684210526</v>
       </c>
       <c r="H523" t="n">
-        <v>0.04476706069755382</v>
+        <v>0.004463090166421241</v>
       </c>
     </row>
     <row r="524">
@@ -16157,7 +16157,7 @@
         <v>4.5</v>
       </c>
       <c r="H524" t="n">
-        <v>0.961990388713382</v>
+        <v>0.3556248266917924</v>
       </c>
     </row>
     <row r="525">
@@ -16187,7 +16187,7 @@
         <v>1.421052631578947</v>
       </c>
       <c r="H525" t="n">
-        <v>0.02006118649825558</v>
+        <v>0.09593535202294187</v>
       </c>
     </row>
     <row r="526">
@@ -16217,7 +16217,7 @@
         <v>6.763157894736842</v>
       </c>
       <c r="H526" t="n">
-        <v>0.9999999999859952</v>
+        <v>0.9999998702001858</v>
       </c>
     </row>
     <row r="527">
@@ -16247,7 +16247,7 @@
         <v>4.763157894736842</v>
       </c>
       <c r="H527" t="n">
-        <v>0.000387708452230379</v>
+        <v>0.001465021027331802</v>
       </c>
     </row>
     <row r="528">
@@ -16277,7 +16277,7 @@
         <v>1.868421052631579</v>
       </c>
       <c r="H528" t="n">
-        <v>0.9999905479729314</v>
+        <v>0.9973858131629826</v>
       </c>
     </row>
     <row r="529">
@@ -16307,7 +16307,7 @@
         <v>1.157894736842105</v>
       </c>
       <c r="H529" t="n">
-        <v>0.9057547173511644</v>
+        <v>0.1355627772518629</v>
       </c>
     </row>
     <row r="530">
@@ -16337,7 +16337,7 @@
         <v>2.631578947368421</v>
       </c>
       <c r="H530" t="n">
-        <v>0.002413876107085454</v>
+        <v>0.001526221888219025</v>
       </c>
     </row>
     <row r="531">
@@ -16367,7 +16367,7 @@
         <v>2.289473684210526</v>
       </c>
       <c r="H531" t="n">
-        <v>0.03861549479122874</v>
+        <v>0.8021933470555834</v>
       </c>
     </row>
     <row r="532">
@@ -16397,7 +16397,7 @@
         <v>3.315789473684211</v>
       </c>
       <c r="H532" t="n">
-        <v>0.9997006968016353</v>
+        <v>0.999706534812828</v>
       </c>
     </row>
     <row r="533">
@@ -16427,7 +16427,7 @@
         <v>4.526315789473684</v>
       </c>
       <c r="H533" t="n">
-        <v>0.002352320812918733</v>
+        <v>0.002128649256962053</v>
       </c>
     </row>
     <row r="534">
@@ -16457,7 +16457,7 @@
         <v>0.8947368421052632</v>
       </c>
       <c r="H534" t="n">
-        <v>0.4661137838953036</v>
+        <v>0.4200427911312146</v>
       </c>
     </row>
     <row r="535">
@@ -16487,7 +16487,7 @@
         <v>1.5</v>
       </c>
       <c r="H535" t="n">
-        <v>0.9993657966763874</v>
+        <v>0.9993402897148373</v>
       </c>
     </row>
     <row r="536">
@@ -16517,7 +16517,7 @@
         <v>7.394736842105263</v>
       </c>
       <c r="H536" t="n">
-        <v>0.4865376945388324</v>
+        <v>0.4725803620636094</v>
       </c>
     </row>
     <row r="537">
@@ -16547,7 +16547,7 @@
         <v>16.57894736842105</v>
       </c>
       <c r="H537" t="n">
-        <v>0.9999994397579975</v>
+        <v>0.9999994099299625</v>
       </c>
     </row>
     <row r="538">
@@ -16577,7 +16577,7 @@
         <v>10.21052631578947</v>
       </c>
       <c r="H538" t="n">
-        <v>0.9974609114218551</v>
+        <v>0.9974018934288147</v>
       </c>
     </row>
     <row r="539">
@@ -16607,7 +16607,7 @@
         <v>22.63157894736842</v>
       </c>
       <c r="H539" t="n">
-        <v>0.9998688843486583</v>
+        <v>0.9998717131350147</v>
       </c>
     </row>
     <row r="540">
@@ -16637,7 +16637,7 @@
         <v>8.789473684210526</v>
       </c>
       <c r="H540" t="n">
-        <v>0.9970858861645215</v>
+        <v>0.9968439404931401</v>
       </c>
     </row>
     <row r="541">
@@ -16667,7 +16667,7 @@
         <v>9.868421052631581</v>
       </c>
       <c r="H541" t="n">
-        <v>0.0008407394948711339</v>
+        <v>0.0007940398634220454</v>
       </c>
     </row>
     <row r="542">
@@ -16697,7 +16697,7 @@
         <v>1.210526315789474</v>
       </c>
       <c r="H542" t="n">
-        <v>0.02341276918981824</v>
+        <v>0.02544412256951272</v>
       </c>
     </row>
     <row r="543">
@@ -16727,7 +16727,7 @@
         <v>16.86842105263158</v>
       </c>
       <c r="H543" t="n">
-        <v>0.2090190011047418</v>
+        <v>0.2190907670005289</v>
       </c>
     </row>
     <row r="544">
@@ -16757,7 +16757,7 @@
         <v>1.473684210526316</v>
       </c>
       <c r="H544" t="n">
-        <v>0.002735159431246838</v>
+        <v>0.003030735657816966</v>
       </c>
     </row>
     <row r="545">
@@ -16787,7 +16787,7 @@
         <v>12.57894736842105</v>
       </c>
       <c r="H545" t="n">
-        <v>0.028772785271764</v>
+        <v>0.02288049036592716</v>
       </c>
     </row>
     <row r="546">
@@ -16817,7 +16817,7 @@
         <v>8.605263157894736</v>
       </c>
       <c r="H546" t="n">
-        <v>0.9976298767526772</v>
+        <v>0.9973532219995721</v>
       </c>
     </row>
     <row r="547">
@@ -16847,7 +16847,7 @@
         <v>0.5789473684210527</v>
       </c>
       <c r="H547" t="n">
-        <v>1.099483064598356e-07</v>
+        <v>1.207572565702192e-07</v>
       </c>
     </row>
     <row r="548">
@@ -16877,7 +16877,7 @@
         <v>45.63157894736842</v>
       </c>
       <c r="H548" t="n">
-        <v>3.479362557969565e-05</v>
+        <v>3.289491586134893e-05</v>
       </c>
     </row>
     <row r="549">
@@ -16907,7 +16907,7 @@
         <v>10.36842105263158</v>
       </c>
       <c r="H549" t="n">
-        <v>0.9970237357855434</v>
+        <v>0.9972750331733209</v>
       </c>
     </row>
     <row r="550">
@@ -16937,7 +16937,7 @@
         <v>1.052631578947368</v>
       </c>
       <c r="H550" t="n">
-        <v>0.99536292057871</v>
+        <v>0.995011190120759</v>
       </c>
     </row>
     <row r="551">
@@ -16967,7 +16967,7 @@
         <v>1.131578947368421</v>
       </c>
       <c r="H551" t="n">
-        <v>0.9610095831188915</v>
+        <v>0.9682879879914467</v>
       </c>
     </row>
     <row r="552">
@@ -16997,7 +16997,7 @@
         <v>5.105263157894737</v>
       </c>
       <c r="H552" t="n">
-        <v>0.4443081293885708</v>
+        <v>0.4547821370604486</v>
       </c>
     </row>
     <row r="553">
@@ -17027,7 +17027,7 @@
         <v>38.86842105263158</v>
       </c>
       <c r="H553" t="n">
-        <v>5.987625804264494e-05</v>
+        <v>6.099191717967393e-05</v>
       </c>
     </row>
     <row r="554">
@@ -17057,7 +17057,7 @@
         <v>5.105263157894737</v>
       </c>
       <c r="H554" t="n">
-        <v>0.0001627398819615663</v>
+        <v>0.0001685979948479287</v>
       </c>
     </row>
     <row r="555">
@@ -17087,7 +17087,7 @@
         <v>23.92105263157895</v>
       </c>
       <c r="H555" t="n">
-        <v>0.9998403615903083</v>
+        <v>0.9998408420274825</v>
       </c>
     </row>
     <row r="556">
@@ -17117,7 +17117,7 @@
         <v>4.162011173184358</v>
       </c>
       <c r="H556" t="n">
-        <v>0.6292860556998959</v>
+        <v>0.5580358536675756</v>
       </c>
     </row>
     <row r="557">
@@ -17147,7 +17147,7 @@
         <v>16.81564245810056</v>
       </c>
       <c r="H557" t="n">
-        <v>0.9833652769520945</v>
+        <v>0.9829915975185035</v>
       </c>
     </row>
     <row r="558">
@@ -17177,7 +17177,7 @@
         <v>2.346368715083799</v>
       </c>
       <c r="H558" t="n">
-        <v>0.9979178478086516</v>
+        <v>0.9992425866284509</v>
       </c>
     </row>
     <row r="559">
@@ -17207,7 +17207,7 @@
         <v>21.4804469273743</v>
       </c>
       <c r="H559" t="n">
-        <v>0.999999999997345</v>
+        <v>0.9999999999978704</v>
       </c>
     </row>
     <row r="560">
@@ -17237,7 +17237,7 @@
         <v>3.743016759776537</v>
       </c>
       <c r="H560" t="n">
-        <v>0.8956321354440866</v>
+        <v>0.9458496426390236</v>
       </c>
     </row>
     <row r="561">
@@ -17267,7 +17267,7 @@
         <v>3.35195530726257</v>
       </c>
       <c r="H561" t="n">
-        <v>0.9542904159424794</v>
+        <v>0.7658541331275422</v>
       </c>
     </row>
     <row r="562">
@@ -17297,7 +17297,7 @@
         <v>15.11173184357542</v>
       </c>
       <c r="H562" t="n">
-        <v>0.001038485048441714</v>
+        <v>0.001380141274902596</v>
       </c>
     </row>
     <row r="563">
@@ -17327,7 +17327,7 @@
         <v>9.301675977653632</v>
       </c>
       <c r="H563" t="n">
-        <v>0.8875405958244608</v>
+        <v>0.8835695436402909</v>
       </c>
     </row>
     <row r="564">
@@ -17357,7 +17357,7 @@
         <v>3.435754189944134</v>
       </c>
       <c r="H564" t="n">
-        <v>0.001819813788793367</v>
+        <v>0.0024441723353216</v>
       </c>
     </row>
     <row r="565">
@@ -17387,7 +17387,7 @@
         <v>62.51396648044693</v>
       </c>
       <c r="H565" t="n">
-        <v>0.9999999996650299</v>
+        <v>0.9999999995927356</v>
       </c>
     </row>
     <row r="566">
@@ -17417,7 +17417,7 @@
         <v>16.731843575419</v>
       </c>
       <c r="H566" t="n">
-        <v>0.116114267049389</v>
+        <v>0.1694152771796467</v>
       </c>
     </row>
     <row r="567">
@@ -17447,7 +17447,7 @@
         <v>5.335195530726257</v>
       </c>
       <c r="H567" t="n">
-        <v>0.02871062788555024</v>
+        <v>0.01256163308184423</v>
       </c>
     </row>
     <row r="568">
@@ -17477,7 +17477,7 @@
         <v>22.0391061452514</v>
       </c>
       <c r="H568" t="n">
-        <v>0.9030165812234368</v>
+        <v>0.913636457856951</v>
       </c>
     </row>
     <row r="569">
@@ -17507,7 +17507,7 @@
         <v>22.54189944134079</v>
       </c>
       <c r="H569" t="n">
-        <v>0.9436395256075807</v>
+        <v>0.9888311728753357</v>
       </c>
     </row>
     <row r="570">
@@ -17537,7 +17537,7 @@
         <v>9.441340782122904</v>
       </c>
       <c r="H570" t="n">
-        <v>0.9926326669630425</v>
+        <v>0.9977266270488012</v>
       </c>
     </row>
     <row r="571">
@@ -17567,7 +17567,7 @@
         <v>44</v>
       </c>
       <c r="H571" t="n">
-        <v>0.9999989276107126</v>
+        <v>0.9999999063456079</v>
       </c>
     </row>
     <row r="572">
@@ -17597,7 +17597,7 @@
         <v>6</v>
       </c>
       <c r="H572" t="n">
-        <v>0.001236715213779644</v>
+        <v>0.1284452684676164</v>
       </c>
     </row>
     <row r="573">
@@ -17627,7 +17627,7 @@
         <v>8</v>
       </c>
       <c r="H573" t="n">
-        <v>2.905786789601154e-05</v>
+        <v>0.0002422887328467014</v>
       </c>
     </row>
     <row r="574">
@@ -17657,7 +17657,7 @@
         <v>32</v>
       </c>
       <c r="H574" t="n">
-        <v>0.9579429407897962</v>
+        <v>0.2962249250624761</v>
       </c>
     </row>
     <row r="575">
@@ -17687,7 +17687,7 @@
         <v>15</v>
       </c>
       <c r="H575" t="n">
-        <v>7.020710047211523e-05</v>
+        <v>0.002468566636851544</v>
       </c>
     </row>
     <row r="576">
@@ -17717,7 +17717,7 @@
         <v>8</v>
       </c>
       <c r="H576" t="n">
-        <v>0.001326745927317677</v>
+        <v>0.003990500683988743</v>
       </c>
     </row>
     <row r="577">
@@ -17747,7 +17747,7 @@
         <v>18</v>
       </c>
       <c r="H577" t="n">
-        <v>0.9932721996726878</v>
+        <v>0.9739394517127272</v>
       </c>
     </row>
     <row r="578">
@@ -17777,7 +17777,7 @@
         <v>7</v>
       </c>
       <c r="H578" t="n">
-        <v>0.006259989984026612</v>
+        <v>0.01662375675211077</v>
       </c>
     </row>
     <row r="579">
@@ -17807,7 +17807,7 @@
         <v>13</v>
       </c>
       <c r="H579" t="n">
-        <v>0.8240633000968648</v>
+        <v>0.4956665519151092</v>
       </c>
     </row>
     <row r="580">
@@ -17837,7 +17837,7 @@
         <v>7</v>
       </c>
       <c r="H580" t="n">
-        <v>0.004129457252036932</v>
+        <v>0.002567652561638504</v>
       </c>
     </row>
     <row r="581">
@@ -17867,7 +17867,7 @@
         <v>5</v>
       </c>
       <c r="H581" t="n">
-        <v>0.329416434462636</v>
+        <v>0.01050787871502718</v>
       </c>
     </row>
     <row r="582">
@@ -17897,7 +17897,7 @@
         <v>18</v>
       </c>
       <c r="H582" t="n">
-        <v>0.004641746753735936</v>
+        <v>0.02586797841538176</v>
       </c>
     </row>
     <row r="583">
@@ -17927,7 +17927,7 @@
         <v>8</v>
       </c>
       <c r="H583" t="n">
-        <v>0.009713824828990634</v>
+        <v>0.002282637617690091</v>
       </c>
     </row>
     <row r="584">
@@ -17957,7 +17957,7 @@
         <v>44</v>
       </c>
       <c r="H584" t="n">
-        <v>0.9999925138514453</v>
+        <v>0.9999994728887681</v>
       </c>
     </row>
     <row r="585">
@@ -17987,7 +17987,7 @@
         <v>11</v>
       </c>
       <c r="H585" t="n">
-        <v>0.9741366516821521</v>
+        <v>0.9989018305211933</v>
       </c>
     </row>
     <row r="586">
@@ -18017,7 +18017,7 @@
         <v>12</v>
       </c>
       <c r="H586" t="n">
-        <v>0.02455945536668656</v>
+        <v>0.01021298434143594</v>
       </c>
     </row>
     <row r="587">
@@ -18047,7 +18047,7 @@
         <v>5</v>
       </c>
       <c r="H587" t="n">
-        <v>2.868925395337328e-07</v>
+        <v>3.267257139017825e-06</v>
       </c>
     </row>
     <row r="588">
@@ -18077,7 +18077,7 @@
         <v>8</v>
       </c>
       <c r="H588" t="n">
-        <v>0.1067864882135107</v>
+        <v>0.002338455965994601</v>
       </c>
     </row>
     <row r="589">
@@ -18107,7 +18107,7 @@
         <v>13</v>
       </c>
       <c r="H589" t="n">
-        <v>0.001454849754989261</v>
+        <v>0.003510714600979511</v>
       </c>
     </row>
     <row r="590">
@@ -18137,7 +18137,7 @@
         <v>4</v>
       </c>
       <c r="H590" t="n">
-        <v>1.048217042819094e-05</v>
+        <v>0.00150866118588695</v>
       </c>
     </row>
     <row r="591">
@@ -18167,7 +18167,7 @@
         <v>5</v>
       </c>
       <c r="H591" t="n">
-        <v>4.816123544732792e-05</v>
+        <v>8.493627350024364e-05</v>
       </c>
     </row>
     <row r="592">
@@ -18197,7 +18197,7 @@
         <v>32</v>
       </c>
       <c r="H592" t="n">
-        <v>0.99966866627302</v>
+        <v>0.9976841713773077</v>
       </c>
     </row>
     <row r="593">
@@ -18227,7 +18227,7 @@
         <v>11</v>
       </c>
       <c r="H593" t="n">
-        <v>0.1744191526148738</v>
+        <v>6.612148760561319e-05</v>
       </c>
     </row>
     <row r="594">
@@ -18257,7 +18257,7 @@
         <v>13</v>
       </c>
       <c r="H594" t="n">
-        <v>0.9908832269735306</v>
+        <v>0.984789219154433</v>
       </c>
     </row>
     <row r="595">
@@ -18287,7 +18287,7 @@
         <v>27</v>
       </c>
       <c r="H595" t="n">
-        <v>0.6463077923497285</v>
+        <v>0.2740928918946223</v>
       </c>
     </row>
     <row r="596">
@@ -18317,7 +18317,7 @@
         <v>14</v>
       </c>
       <c r="H596" t="n">
-        <v>0.6356756979081364</v>
+        <v>0.1962319469545977</v>
       </c>
     </row>
     <row r="597">
@@ -18347,7 +18347,7 @@
         <v>8</v>
       </c>
       <c r="H597" t="n">
-        <v>0.0003442665517691705</v>
+        <v>0.9237320204425741</v>
       </c>
     </row>
     <row r="598">
@@ -18377,7 +18377,7 @@
         <v>1</v>
       </c>
       <c r="H598" t="n">
-        <v>0.000870545382303095</v>
+        <v>0.1323843679847133</v>
       </c>
     </row>
     <row r="599">
@@ -18407,7 +18407,7 @@
         <v>21</v>
       </c>
       <c r="H599" t="n">
-        <v>0.9145324210108157</v>
+        <v>0.1781499334925116</v>
       </c>
     </row>
     <row r="600">
@@ -18437,7 +18437,7 @@
         <v>8</v>
       </c>
       <c r="H600" t="n">
-        <v>0.0005860652399675094</v>
+        <v>0.007058771808907969</v>
       </c>
     </row>
     <row r="601">
@@ -18467,7 +18467,7 @@
         <v>11</v>
       </c>
       <c r="H601" t="n">
-        <v>7.675649108318171e-06</v>
+        <v>9.746673223443655e-06</v>
       </c>
     </row>
     <row r="602">
@@ -18497,7 +18497,7 @@
         <v>5</v>
       </c>
       <c r="H602" t="n">
-        <v>0.0006856587809616929</v>
+        <v>0.0002437616708703583</v>
       </c>
     </row>
     <row r="603">
@@ -18527,7 +18527,7 @@
         <v>8</v>
       </c>
       <c r="H603" t="n">
-        <v>0.006399964184066597</v>
+        <v>0.002127357124811556</v>
       </c>
     </row>
     <row r="604">
@@ -18557,7 +18557,7 @@
         <v>5</v>
       </c>
       <c r="H604" t="n">
-        <v>0.00112184137153091</v>
+        <v>1.430627968444622e-05</v>
       </c>
     </row>
     <row r="605">
@@ -18587,7 +18587,7 @@
         <v>6</v>
       </c>
       <c r="H605" t="n">
-        <v>0.01310056018612227</v>
+        <v>0.0001528396002937508</v>
       </c>
     </row>
     <row r="606">
@@ -18617,7 +18617,7 @@
         <v>8</v>
       </c>
       <c r="H606" t="n">
-        <v>0.3569188276207576</v>
+        <v>0.3915118408682672</v>
       </c>
     </row>
     <row r="607">
@@ -18647,7 +18647,7 @@
         <v>8</v>
       </c>
       <c r="H607" t="n">
-        <v>0.9991002844142163</v>
+        <v>0.997190022278738</v>
       </c>
     </row>
     <row r="608">
@@ -18677,7 +18677,7 @@
         <v>3</v>
       </c>
       <c r="H608" t="n">
-        <v>0.005695946516728425</v>
+        <v>0.0001833944033524954</v>
       </c>
     </row>
     <row r="609">
@@ -18707,7 +18707,7 @@
         <v>8</v>
       </c>
       <c r="H609" t="n">
-        <v>0.002568093770765805</v>
+        <v>0.001289472813385353</v>
       </c>
     </row>
     <row r="610">
@@ -18737,7 +18737,7 @@
         <v>8</v>
       </c>
       <c r="H610" t="n">
-        <v>1.072993485858463e-05</v>
+        <v>0.0002252568068461746</v>
       </c>
     </row>
     <row r="611">
@@ -18767,7 +18767,7 @@
         <v>4</v>
       </c>
       <c r="H611" t="n">
-        <v>0.200577357538157</v>
+        <v>0.00698607515291997</v>
       </c>
     </row>
     <row r="612">
@@ -18797,7 +18797,7 @@
         <v>8</v>
       </c>
       <c r="H612" t="n">
-        <v>4.762856302530918e-05</v>
+        <v>0.004643743667930977</v>
       </c>
     </row>
     <row r="613">
@@ -18827,7 +18827,7 @@
         <v>5</v>
       </c>
       <c r="H613" t="n">
-        <v>0.1417385708703188</v>
+        <v>0.03114449041977773</v>
       </c>
     </row>
     <row r="614">
@@ -18857,7 +18857,7 @@
         <v>16</v>
       </c>
       <c r="H614" t="n">
-        <v>0.006553316480733715</v>
+        <v>0.03632723366522188</v>
       </c>
     </row>
     <row r="615">
@@ -18887,7 +18887,7 @@
         <v>20</v>
       </c>
       <c r="H615" t="n">
-        <v>0.9945964665217861</v>
+        <v>0.9994103338776512</v>
       </c>
     </row>
     <row r="616">
@@ -18917,7 +18917,7 @@
         <v>6</v>
       </c>
       <c r="H616" t="n">
-        <v>1.411666856967931e-05</v>
+        <v>9.749387191709295e-05</v>
       </c>
     </row>
     <row r="617">
@@ -18947,7 +18947,7 @@
         <v>3</v>
       </c>
       <c r="H617" t="n">
-        <v>0.01511828504243006</v>
+        <v>1.299509843255318e-05</v>
       </c>
     </row>
     <row r="618">
@@ -18977,7 +18977,7 @@
         <v>5</v>
       </c>
       <c r="H618" t="n">
-        <v>0.000769544241066376</v>
+        <v>0.004902014116214006</v>
       </c>
     </row>
     <row r="619">
@@ -19007,7 +19007,7 @@
         <v>8</v>
       </c>
       <c r="H619" t="n">
-        <v>0.8069645095466172</v>
+        <v>0.9283967185234447</v>
       </c>
     </row>
     <row r="620">
@@ -19037,7 +19037,7 @@
         <v>4</v>
       </c>
       <c r="H620" t="n">
-        <v>0.01497540219084521</v>
+        <v>0.0002148669832824065</v>
       </c>
     </row>
     <row r="621">
@@ -19067,7 +19067,7 @@
         <v>7</v>
       </c>
       <c r="H621" t="n">
-        <v>0.9955350103683398</v>
+        <v>0.9480151285165137</v>
       </c>
     </row>
     <row r="622">
@@ -19097,7 +19097,7 @@
         <v>8</v>
       </c>
       <c r="H622" t="n">
-        <v>5.3950097924391e-05</v>
+        <v>0.002787776779521643</v>
       </c>
     </row>
     <row r="623">
@@ -19127,7 +19127,7 @@
         <v>24</v>
       </c>
       <c r="H623" t="n">
-        <v>0.4875684978305959</v>
+        <v>0.9789597505746949</v>
       </c>
     </row>
     <row r="624">
@@ -19157,7 +19157,7 @@
         <v>5</v>
       </c>
       <c r="H624" t="n">
-        <v>0.000292921890719187</v>
+        <v>3.194154475611814e-05</v>
       </c>
     </row>
     <row r="625">
@@ -19187,7 +19187,7 @@
         <v>1</v>
       </c>
       <c r="H625" t="n">
-        <v>5.160449154648477e-08</v>
+        <v>1.477133189083161e-06</v>
       </c>
     </row>
     <row r="626">
@@ -19217,7 +19217,7 @@
         <v>14</v>
       </c>
       <c r="H626" t="n">
-        <v>0.01152153592738162</v>
+        <v>0.04929492216476329</v>
       </c>
     </row>
     <row r="627">
@@ -19247,7 +19247,7 @@
         <v>14</v>
       </c>
       <c r="H627" t="n">
-        <v>0.9943546222159848</v>
+        <v>0.9962041174802916</v>
       </c>
     </row>
     <row r="628">
@@ -19277,7 +19277,7 @@
         <v>8</v>
       </c>
       <c r="H628" t="n">
-        <v>0.9291794343100275</v>
+        <v>0.2584574476531192</v>
       </c>
     </row>
     <row r="629">
@@ -19307,7 +19307,7 @@
         <v>5</v>
       </c>
       <c r="H629" t="n">
-        <v>0.009293058168639335</v>
+        <v>1.704166950052321e-05</v>
       </c>
     </row>
   </sheetData>
